--- a/product-definitions/spreadsheet/cloud-coverage.xlsx
+++ b/product-definitions/spreadsheet/cloud-coverage.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="global-attributes-specific" sheetId="1" r:id="rId3"/>
-    <sheet state="visible" name="dimensions-specific" sheetId="2" r:id="rId4"/>
-    <sheet state="visible" name="variables-specific" sheetId="3" r:id="rId5"/>
+    <sheet state="visible" name="global-attributes-specific" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="dimensions-specific" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="variables-specific" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="94">
   <si>
     <t>Name</t>
   </si>
@@ -258,7 +258,7 @@
     <t>Window Contamination (mV as measured by ADC: 0 - 2500)</t>
   </si>
   <si>
-    <t>window_transmttance</t>
+    <t>window_transmittance</t>
   </si>
   <si>
     <t>Window Transmittance, % of nominal value</t>
@@ -280,9 +280,6 @@
   </si>
   <si>
     <t>qc_flag</t>
-  </si>
-  <si>
-    <t>time. layer_index</t>
   </si>
   <si>
     <t>Data Quality flag</t>
@@ -310,11 +307,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -323,18 +321,29 @@
     </font>
     <font>
       <b/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font/>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
     <font>
       <b/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -364,16 +373,13 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border/>
-    <border>
-      <right/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="26">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -389,29 +395,19 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -420,53 +416,39 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="top"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -488,17 +470,212 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+  <a:themeElements>
+    <a:clrScheme name="Sheets">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="0000FF"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Sheets">
+      <a:majorFont>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="2" width="29.43"/>
-    <col customWidth="1" min="3" max="3" width="29.29"/>
-    <col customWidth="1" min="5" max="5" width="29.57"/>
-    <col customWidth="1" min="6" max="6" width="29.43"/>
+    <col customWidth="1" min="1" max="2" width="25.75"/>
+    <col customWidth="1" min="3" max="3" width="25.63"/>
+    <col customWidth="1" min="4" max="4" width="12.63"/>
+    <col customWidth="1" min="5" max="5" width="25.88"/>
+    <col customWidth="1" min="6" max="6" width="25.75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -548,7 +725,7 @@
       <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="4"/>
@@ -578,13 +755,13 @@
       <c r="Z2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="4"/>
@@ -620,7 +797,7 @@
       <c r="B4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -634,7 +811,7 @@
       <c r="B5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -648,7 +825,7 @@
       <c r="B6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -662,7 +839,7 @@
       <c r="B7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -676,13 +853,993 @@
       <c r="B8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>9</v>
       </c>
     </row>
+    <row r="21" ht="15.75" customHeight="1"/>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -693,81 +1850,75 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.57"/>
-    <col customWidth="1" min="2" max="2" width="18.14"/>
-    <col customWidth="1" min="3" max="3" width="45.57"/>
-    <col customWidth="1" min="4" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="15.38"/>
+    <col customWidth="1" min="2" max="2" width="15.88"/>
+    <col customWidth="1" min="3" max="3" width="39.88"/>
+    <col customWidth="1" min="4" max="23" width="7.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.0" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
     </row>
     <row r="2" ht="12.0" customHeight="1">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>1.0</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="13"/>
-      <c r="S2" s="13"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="13"/>
-      <c r="W2" s="13"/>
-      <c r="X2" s="13"/>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="13"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="11"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
+      <c r="N2" s="11"/>
+      <c r="O2" s="11"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
     </row>
     <row r="3" ht="12.0" customHeight="1"/>
     <row r="4" ht="12.0" customHeight="1"/>
@@ -987,786 +2138,786 @@
     <row r="218" ht="12.0" customHeight="1"/>
     <row r="219" ht="12.0" customHeight="1"/>
     <row r="220" ht="12.0" customHeight="1"/>
-    <row r="221" ht="12.0" customHeight="1"/>
-    <row r="222" ht="12.0" customHeight="1"/>
-    <row r="223" ht="12.0" customHeight="1"/>
-    <row r="224" ht="12.0" customHeight="1"/>
-    <row r="225" ht="12.0" customHeight="1"/>
-    <row r="226" ht="12.0" customHeight="1"/>
-    <row r="227" ht="12.0" customHeight="1"/>
-    <row r="228" ht="12.0" customHeight="1"/>
-    <row r="229" ht="12.0" customHeight="1"/>
-    <row r="230" ht="12.0" customHeight="1"/>
-    <row r="231" ht="12.0" customHeight="1"/>
-    <row r="232" ht="12.0" customHeight="1"/>
-    <row r="233" ht="12.0" customHeight="1"/>
-    <row r="234" ht="12.0" customHeight="1"/>
-    <row r="235" ht="12.0" customHeight="1"/>
-    <row r="236" ht="12.0" customHeight="1"/>
-    <row r="237" ht="12.0" customHeight="1"/>
-    <row r="238" ht="12.0" customHeight="1"/>
-    <row r="239" ht="12.0" customHeight="1"/>
-    <row r="240" ht="12.0" customHeight="1"/>
-    <row r="241" ht="12.0" customHeight="1"/>
-    <row r="242" ht="12.0" customHeight="1"/>
-    <row r="243" ht="12.0" customHeight="1"/>
-    <row r="244" ht="12.0" customHeight="1"/>
-    <row r="245" ht="12.0" customHeight="1"/>
-    <row r="246" ht="12.0" customHeight="1"/>
-    <row r="247" ht="12.0" customHeight="1"/>
-    <row r="248" ht="12.0" customHeight="1"/>
-    <row r="249" ht="12.0" customHeight="1"/>
-    <row r="250" ht="12.0" customHeight="1"/>
-    <row r="251" ht="12.0" customHeight="1"/>
-    <row r="252" ht="12.0" customHeight="1"/>
-    <row r="253" ht="12.0" customHeight="1"/>
-    <row r="254" ht="12.0" customHeight="1"/>
-    <row r="255" ht="12.0" customHeight="1"/>
-    <row r="256" ht="12.0" customHeight="1"/>
-    <row r="257" ht="12.0" customHeight="1"/>
-    <row r="258" ht="12.0" customHeight="1"/>
-    <row r="259" ht="12.0" customHeight="1"/>
-    <row r="260" ht="12.0" customHeight="1"/>
-    <row r="261" ht="12.0" customHeight="1"/>
-    <row r="262" ht="12.0" customHeight="1"/>
-    <row r="263" ht="12.0" customHeight="1"/>
-    <row r="264" ht="12.0" customHeight="1"/>
-    <row r="265" ht="12.0" customHeight="1"/>
-    <row r="266" ht="12.0" customHeight="1"/>
-    <row r="267" ht="12.0" customHeight="1"/>
-    <row r="268" ht="12.0" customHeight="1"/>
-    <row r="269" ht="12.0" customHeight="1"/>
-    <row r="270" ht="12.0" customHeight="1"/>
-    <row r="271" ht="12.0" customHeight="1"/>
-    <row r="272" ht="12.0" customHeight="1"/>
-    <row r="273" ht="12.0" customHeight="1"/>
-    <row r="274" ht="12.0" customHeight="1"/>
-    <row r="275" ht="12.0" customHeight="1"/>
-    <row r="276" ht="12.0" customHeight="1"/>
-    <row r="277" ht="12.0" customHeight="1"/>
-    <row r="278" ht="12.0" customHeight="1"/>
-    <row r="279" ht="12.0" customHeight="1"/>
-    <row r="280" ht="12.0" customHeight="1"/>
-    <row r="281" ht="12.0" customHeight="1"/>
-    <row r="282" ht="12.0" customHeight="1"/>
-    <row r="283" ht="12.0" customHeight="1"/>
-    <row r="284" ht="12.0" customHeight="1"/>
-    <row r="285" ht="12.0" customHeight="1"/>
-    <row r="286" ht="12.0" customHeight="1"/>
-    <row r="287" ht="12.0" customHeight="1"/>
-    <row r="288" ht="12.0" customHeight="1"/>
-    <row r="289" ht="12.0" customHeight="1"/>
-    <row r="290" ht="12.0" customHeight="1"/>
-    <row r="291" ht="12.0" customHeight="1"/>
-    <row r="292" ht="12.0" customHeight="1"/>
-    <row r="293" ht="12.0" customHeight="1"/>
-    <row r="294" ht="12.0" customHeight="1"/>
-    <row r="295" ht="12.0" customHeight="1"/>
-    <row r="296" ht="12.0" customHeight="1"/>
-    <row r="297" ht="12.0" customHeight="1"/>
-    <row r="298" ht="12.0" customHeight="1"/>
-    <row r="299" ht="12.0" customHeight="1"/>
-    <row r="300" ht="12.0" customHeight="1"/>
-    <row r="301" ht="12.0" customHeight="1"/>
-    <row r="302" ht="12.0" customHeight="1"/>
-    <row r="303" ht="12.0" customHeight="1"/>
-    <row r="304" ht="12.0" customHeight="1"/>
-    <row r="305" ht="12.0" customHeight="1"/>
-    <row r="306" ht="12.0" customHeight="1"/>
-    <row r="307" ht="12.0" customHeight="1"/>
-    <row r="308" ht="12.0" customHeight="1"/>
-    <row r="309" ht="12.0" customHeight="1"/>
-    <row r="310" ht="12.0" customHeight="1"/>
-    <row r="311" ht="12.0" customHeight="1"/>
-    <row r="312" ht="12.0" customHeight="1"/>
-    <row r="313" ht="12.0" customHeight="1"/>
-    <row r="314" ht="12.0" customHeight="1"/>
-    <row r="315" ht="12.0" customHeight="1"/>
-    <row r="316" ht="12.0" customHeight="1"/>
-    <row r="317" ht="12.0" customHeight="1"/>
-    <row r="318" ht="12.0" customHeight="1"/>
-    <row r="319" ht="12.0" customHeight="1"/>
-    <row r="320" ht="12.0" customHeight="1"/>
-    <row r="321" ht="12.0" customHeight="1"/>
-    <row r="322" ht="12.0" customHeight="1"/>
-    <row r="323" ht="12.0" customHeight="1"/>
-    <row r="324" ht="12.0" customHeight="1"/>
-    <row r="325" ht="12.0" customHeight="1"/>
-    <row r="326" ht="12.0" customHeight="1"/>
-    <row r="327" ht="12.0" customHeight="1"/>
-    <row r="328" ht="12.0" customHeight="1"/>
-    <row r="329" ht="12.0" customHeight="1"/>
-    <row r="330" ht="12.0" customHeight="1"/>
-    <row r="331" ht="12.0" customHeight="1"/>
-    <row r="332" ht="12.0" customHeight="1"/>
-    <row r="333" ht="12.0" customHeight="1"/>
-    <row r="334" ht="12.0" customHeight="1"/>
-    <row r="335" ht="12.0" customHeight="1"/>
-    <row r="336" ht="12.0" customHeight="1"/>
-    <row r="337" ht="12.0" customHeight="1"/>
-    <row r="338" ht="12.0" customHeight="1"/>
-    <row r="339" ht="12.0" customHeight="1"/>
-    <row r="340" ht="12.0" customHeight="1"/>
-    <row r="341" ht="12.0" customHeight="1"/>
-    <row r="342" ht="12.0" customHeight="1"/>
-    <row r="343" ht="12.0" customHeight="1"/>
-    <row r="344" ht="12.0" customHeight="1"/>
-    <row r="345" ht="12.0" customHeight="1"/>
-    <row r="346" ht="12.0" customHeight="1"/>
-    <row r="347" ht="12.0" customHeight="1"/>
-    <row r="348" ht="12.0" customHeight="1"/>
-    <row r="349" ht="12.0" customHeight="1"/>
-    <row r="350" ht="12.0" customHeight="1"/>
-    <row r="351" ht="12.0" customHeight="1"/>
-    <row r="352" ht="12.0" customHeight="1"/>
-    <row r="353" ht="12.0" customHeight="1"/>
-    <row r="354" ht="12.0" customHeight="1"/>
-    <row r="355" ht="12.0" customHeight="1"/>
-    <row r="356" ht="12.0" customHeight="1"/>
-    <row r="357" ht="12.0" customHeight="1"/>
-    <row r="358" ht="12.0" customHeight="1"/>
-    <row r="359" ht="12.0" customHeight="1"/>
-    <row r="360" ht="12.0" customHeight="1"/>
-    <row r="361" ht="12.0" customHeight="1"/>
-    <row r="362" ht="12.0" customHeight="1"/>
-    <row r="363" ht="12.0" customHeight="1"/>
-    <row r="364" ht="12.0" customHeight="1"/>
-    <row r="365" ht="12.0" customHeight="1"/>
-    <row r="366" ht="12.0" customHeight="1"/>
-    <row r="367" ht="12.0" customHeight="1"/>
-    <row r="368" ht="12.0" customHeight="1"/>
-    <row r="369" ht="12.0" customHeight="1"/>
-    <row r="370" ht="12.0" customHeight="1"/>
-    <row r="371" ht="12.0" customHeight="1"/>
-    <row r="372" ht="12.0" customHeight="1"/>
-    <row r="373" ht="12.0" customHeight="1"/>
-    <row r="374" ht="12.0" customHeight="1"/>
-    <row r="375" ht="12.0" customHeight="1"/>
-    <row r="376" ht="12.0" customHeight="1"/>
-    <row r="377" ht="12.0" customHeight="1"/>
-    <row r="378" ht="12.0" customHeight="1"/>
-    <row r="379" ht="12.0" customHeight="1"/>
-    <row r="380" ht="12.0" customHeight="1"/>
-    <row r="381" ht="12.0" customHeight="1"/>
-    <row r="382" ht="12.0" customHeight="1"/>
-    <row r="383" ht="12.0" customHeight="1"/>
-    <row r="384" ht="12.0" customHeight="1"/>
-    <row r="385" ht="12.0" customHeight="1"/>
-    <row r="386" ht="12.0" customHeight="1"/>
-    <row r="387" ht="12.0" customHeight="1"/>
-    <row r="388" ht="12.0" customHeight="1"/>
-    <row r="389" ht="12.0" customHeight="1"/>
-    <row r="390" ht="12.0" customHeight="1"/>
-    <row r="391" ht="12.0" customHeight="1"/>
-    <row r="392" ht="12.0" customHeight="1"/>
-    <row r="393" ht="12.0" customHeight="1"/>
-    <row r="394" ht="12.0" customHeight="1"/>
-    <row r="395" ht="12.0" customHeight="1"/>
-    <row r="396" ht="12.0" customHeight="1"/>
-    <row r="397" ht="12.0" customHeight="1"/>
-    <row r="398" ht="12.0" customHeight="1"/>
-    <row r="399" ht="12.0" customHeight="1"/>
-    <row r="400" ht="12.0" customHeight="1"/>
-    <row r="401" ht="12.0" customHeight="1"/>
-    <row r="402" ht="12.0" customHeight="1"/>
-    <row r="403" ht="12.0" customHeight="1"/>
-    <row r="404" ht="12.0" customHeight="1"/>
-    <row r="405" ht="12.0" customHeight="1"/>
-    <row r="406" ht="12.0" customHeight="1"/>
-    <row r="407" ht="12.0" customHeight="1"/>
-    <row r="408" ht="12.0" customHeight="1"/>
-    <row r="409" ht="12.0" customHeight="1"/>
-    <row r="410" ht="12.0" customHeight="1"/>
-    <row r="411" ht="12.0" customHeight="1"/>
-    <row r="412" ht="12.0" customHeight="1"/>
-    <row r="413" ht="12.0" customHeight="1"/>
-    <row r="414" ht="12.0" customHeight="1"/>
-    <row r="415" ht="12.0" customHeight="1"/>
-    <row r="416" ht="12.0" customHeight="1"/>
-    <row r="417" ht="12.0" customHeight="1"/>
-    <row r="418" ht="12.0" customHeight="1"/>
-    <row r="419" ht="12.0" customHeight="1"/>
-    <row r="420" ht="12.0" customHeight="1"/>
-    <row r="421" ht="12.0" customHeight="1"/>
-    <row r="422" ht="12.0" customHeight="1"/>
-    <row r="423" ht="12.0" customHeight="1"/>
-    <row r="424" ht="12.0" customHeight="1"/>
-    <row r="425" ht="12.0" customHeight="1"/>
-    <row r="426" ht="12.0" customHeight="1"/>
-    <row r="427" ht="12.0" customHeight="1"/>
-    <row r="428" ht="12.0" customHeight="1"/>
-    <row r="429" ht="12.0" customHeight="1"/>
-    <row r="430" ht="12.0" customHeight="1"/>
-    <row r="431" ht="12.0" customHeight="1"/>
-    <row r="432" ht="12.0" customHeight="1"/>
-    <row r="433" ht="12.0" customHeight="1"/>
-    <row r="434" ht="12.0" customHeight="1"/>
-    <row r="435" ht="12.0" customHeight="1"/>
-    <row r="436" ht="12.0" customHeight="1"/>
-    <row r="437" ht="12.0" customHeight="1"/>
-    <row r="438" ht="12.0" customHeight="1"/>
-    <row r="439" ht="12.0" customHeight="1"/>
-    <row r="440" ht="12.0" customHeight="1"/>
-    <row r="441" ht="12.0" customHeight="1"/>
-    <row r="442" ht="12.0" customHeight="1"/>
-    <row r="443" ht="12.0" customHeight="1"/>
-    <row r="444" ht="12.0" customHeight="1"/>
-    <row r="445" ht="12.0" customHeight="1"/>
-    <row r="446" ht="12.0" customHeight="1"/>
-    <row r="447" ht="12.0" customHeight="1"/>
-    <row r="448" ht="12.0" customHeight="1"/>
-    <row r="449" ht="12.0" customHeight="1"/>
-    <row r="450" ht="12.0" customHeight="1"/>
-    <row r="451" ht="12.0" customHeight="1"/>
-    <row r="452" ht="12.0" customHeight="1"/>
-    <row r="453" ht="12.0" customHeight="1"/>
-    <row r="454" ht="12.0" customHeight="1"/>
-    <row r="455" ht="12.0" customHeight="1"/>
-    <row r="456" ht="12.0" customHeight="1"/>
-    <row r="457" ht="12.0" customHeight="1"/>
-    <row r="458" ht="12.0" customHeight="1"/>
-    <row r="459" ht="12.0" customHeight="1"/>
-    <row r="460" ht="12.0" customHeight="1"/>
-    <row r="461" ht="12.0" customHeight="1"/>
-    <row r="462" ht="12.0" customHeight="1"/>
-    <row r="463" ht="12.0" customHeight="1"/>
-    <row r="464" ht="12.0" customHeight="1"/>
-    <row r="465" ht="12.0" customHeight="1"/>
-    <row r="466" ht="12.0" customHeight="1"/>
-    <row r="467" ht="12.0" customHeight="1"/>
-    <row r="468" ht="12.0" customHeight="1"/>
-    <row r="469" ht="12.0" customHeight="1"/>
-    <row r="470" ht="12.0" customHeight="1"/>
-    <row r="471" ht="12.0" customHeight="1"/>
-    <row r="472" ht="12.0" customHeight="1"/>
-    <row r="473" ht="12.0" customHeight="1"/>
-    <row r="474" ht="12.0" customHeight="1"/>
-    <row r="475" ht="12.0" customHeight="1"/>
-    <row r="476" ht="12.0" customHeight="1"/>
-    <row r="477" ht="12.0" customHeight="1"/>
-    <row r="478" ht="12.0" customHeight="1"/>
-    <row r="479" ht="12.0" customHeight="1"/>
-    <row r="480" ht="12.0" customHeight="1"/>
-    <row r="481" ht="12.0" customHeight="1"/>
-    <row r="482" ht="12.0" customHeight="1"/>
-    <row r="483" ht="12.0" customHeight="1"/>
-    <row r="484" ht="12.0" customHeight="1"/>
-    <row r="485" ht="12.0" customHeight="1"/>
-    <row r="486" ht="12.0" customHeight="1"/>
-    <row r="487" ht="12.0" customHeight="1"/>
-    <row r="488" ht="12.0" customHeight="1"/>
-    <row r="489" ht="12.0" customHeight="1"/>
-    <row r="490" ht="12.0" customHeight="1"/>
-    <row r="491" ht="12.0" customHeight="1"/>
-    <row r="492" ht="12.0" customHeight="1"/>
-    <row r="493" ht="12.0" customHeight="1"/>
-    <row r="494" ht="12.0" customHeight="1"/>
-    <row r="495" ht="12.0" customHeight="1"/>
-    <row r="496" ht="12.0" customHeight="1"/>
-    <row r="497" ht="12.0" customHeight="1"/>
-    <row r="498" ht="12.0" customHeight="1"/>
-    <row r="499" ht="12.0" customHeight="1"/>
-    <row r="500" ht="12.0" customHeight="1"/>
-    <row r="501" ht="12.0" customHeight="1"/>
-    <row r="502" ht="12.0" customHeight="1"/>
-    <row r="503" ht="12.0" customHeight="1"/>
-    <row r="504" ht="12.0" customHeight="1"/>
-    <row r="505" ht="12.0" customHeight="1"/>
-    <row r="506" ht="12.0" customHeight="1"/>
-    <row r="507" ht="12.0" customHeight="1"/>
-    <row r="508" ht="12.0" customHeight="1"/>
-    <row r="509" ht="12.0" customHeight="1"/>
-    <row r="510" ht="12.0" customHeight="1"/>
-    <row r="511" ht="12.0" customHeight="1"/>
-    <row r="512" ht="12.0" customHeight="1"/>
-    <row r="513" ht="12.0" customHeight="1"/>
-    <row r="514" ht="12.0" customHeight="1"/>
-    <row r="515" ht="12.0" customHeight="1"/>
-    <row r="516" ht="12.0" customHeight="1"/>
-    <row r="517" ht="12.0" customHeight="1"/>
-    <row r="518" ht="12.0" customHeight="1"/>
-    <row r="519" ht="12.0" customHeight="1"/>
-    <row r="520" ht="12.0" customHeight="1"/>
-    <row r="521" ht="12.0" customHeight="1"/>
-    <row r="522" ht="12.0" customHeight="1"/>
-    <row r="523" ht="12.0" customHeight="1"/>
-    <row r="524" ht="12.0" customHeight="1"/>
-    <row r="525" ht="12.0" customHeight="1"/>
-    <row r="526" ht="12.0" customHeight="1"/>
-    <row r="527" ht="12.0" customHeight="1"/>
-    <row r="528" ht="12.0" customHeight="1"/>
-    <row r="529" ht="12.0" customHeight="1"/>
-    <row r="530" ht="12.0" customHeight="1"/>
-    <row r="531" ht="12.0" customHeight="1"/>
-    <row r="532" ht="12.0" customHeight="1"/>
-    <row r="533" ht="12.0" customHeight="1"/>
-    <row r="534" ht="12.0" customHeight="1"/>
-    <row r="535" ht="12.0" customHeight="1"/>
-    <row r="536" ht="12.0" customHeight="1"/>
-    <row r="537" ht="12.0" customHeight="1"/>
-    <row r="538" ht="12.0" customHeight="1"/>
-    <row r="539" ht="12.0" customHeight="1"/>
-    <row r="540" ht="12.0" customHeight="1"/>
-    <row r="541" ht="12.0" customHeight="1"/>
-    <row r="542" ht="12.0" customHeight="1"/>
-    <row r="543" ht="12.0" customHeight="1"/>
-    <row r="544" ht="12.0" customHeight="1"/>
-    <row r="545" ht="12.0" customHeight="1"/>
-    <row r="546" ht="12.0" customHeight="1"/>
-    <row r="547" ht="12.0" customHeight="1"/>
-    <row r="548" ht="12.0" customHeight="1"/>
-    <row r="549" ht="12.0" customHeight="1"/>
-    <row r="550" ht="12.0" customHeight="1"/>
-    <row r="551" ht="12.0" customHeight="1"/>
-    <row r="552" ht="12.0" customHeight="1"/>
-    <row r="553" ht="12.0" customHeight="1"/>
-    <row r="554" ht="12.0" customHeight="1"/>
-    <row r="555" ht="12.0" customHeight="1"/>
-    <row r="556" ht="12.0" customHeight="1"/>
-    <row r="557" ht="12.0" customHeight="1"/>
-    <row r="558" ht="12.0" customHeight="1"/>
-    <row r="559" ht="12.0" customHeight="1"/>
-    <row r="560" ht="12.0" customHeight="1"/>
-    <row r="561" ht="12.0" customHeight="1"/>
-    <row r="562" ht="12.0" customHeight="1"/>
-    <row r="563" ht="12.0" customHeight="1"/>
-    <row r="564" ht="12.0" customHeight="1"/>
-    <row r="565" ht="12.0" customHeight="1"/>
-    <row r="566" ht="12.0" customHeight="1"/>
-    <row r="567" ht="12.0" customHeight="1"/>
-    <row r="568" ht="12.0" customHeight="1"/>
-    <row r="569" ht="12.0" customHeight="1"/>
-    <row r="570" ht="12.0" customHeight="1"/>
-    <row r="571" ht="12.0" customHeight="1"/>
-    <row r="572" ht="12.0" customHeight="1"/>
-    <row r="573" ht="12.0" customHeight="1"/>
-    <row r="574" ht="12.0" customHeight="1"/>
-    <row r="575" ht="12.0" customHeight="1"/>
-    <row r="576" ht="12.0" customHeight="1"/>
-    <row r="577" ht="12.0" customHeight="1"/>
-    <row r="578" ht="12.0" customHeight="1"/>
-    <row r="579" ht="12.0" customHeight="1"/>
-    <row r="580" ht="12.0" customHeight="1"/>
-    <row r="581" ht="12.0" customHeight="1"/>
-    <row r="582" ht="12.0" customHeight="1"/>
-    <row r="583" ht="12.0" customHeight="1"/>
-    <row r="584" ht="12.0" customHeight="1"/>
-    <row r="585" ht="12.0" customHeight="1"/>
-    <row r="586" ht="12.0" customHeight="1"/>
-    <row r="587" ht="12.0" customHeight="1"/>
-    <row r="588" ht="12.0" customHeight="1"/>
-    <row r="589" ht="12.0" customHeight="1"/>
-    <row r="590" ht="12.0" customHeight="1"/>
-    <row r="591" ht="12.0" customHeight="1"/>
-    <row r="592" ht="12.0" customHeight="1"/>
-    <row r="593" ht="12.0" customHeight="1"/>
-    <row r="594" ht="12.0" customHeight="1"/>
-    <row r="595" ht="12.0" customHeight="1"/>
-    <row r="596" ht="12.0" customHeight="1"/>
-    <row r="597" ht="12.0" customHeight="1"/>
-    <row r="598" ht="12.0" customHeight="1"/>
-    <row r="599" ht="12.0" customHeight="1"/>
-    <row r="600" ht="12.0" customHeight="1"/>
-    <row r="601" ht="12.0" customHeight="1"/>
-    <row r="602" ht="12.0" customHeight="1"/>
-    <row r="603" ht="12.0" customHeight="1"/>
-    <row r="604" ht="12.0" customHeight="1"/>
-    <row r="605" ht="12.0" customHeight="1"/>
-    <row r="606" ht="12.0" customHeight="1"/>
-    <row r="607" ht="12.0" customHeight="1"/>
-    <row r="608" ht="12.0" customHeight="1"/>
-    <row r="609" ht="12.0" customHeight="1"/>
-    <row r="610" ht="12.0" customHeight="1"/>
-    <row r="611" ht="12.0" customHeight="1"/>
-    <row r="612" ht="12.0" customHeight="1"/>
-    <row r="613" ht="12.0" customHeight="1"/>
-    <row r="614" ht="12.0" customHeight="1"/>
-    <row r="615" ht="12.0" customHeight="1"/>
-    <row r="616" ht="12.0" customHeight="1"/>
-    <row r="617" ht="12.0" customHeight="1"/>
-    <row r="618" ht="12.0" customHeight="1"/>
-    <row r="619" ht="12.0" customHeight="1"/>
-    <row r="620" ht="12.0" customHeight="1"/>
-    <row r="621" ht="12.0" customHeight="1"/>
-    <row r="622" ht="12.0" customHeight="1"/>
-    <row r="623" ht="12.0" customHeight="1"/>
-    <row r="624" ht="12.0" customHeight="1"/>
-    <row r="625" ht="12.0" customHeight="1"/>
-    <row r="626" ht="12.0" customHeight="1"/>
-    <row r="627" ht="12.0" customHeight="1"/>
-    <row r="628" ht="12.0" customHeight="1"/>
-    <row r="629" ht="12.0" customHeight="1"/>
-    <row r="630" ht="12.0" customHeight="1"/>
-    <row r="631" ht="12.0" customHeight="1"/>
-    <row r="632" ht="12.0" customHeight="1"/>
-    <row r="633" ht="12.0" customHeight="1"/>
-    <row r="634" ht="12.0" customHeight="1"/>
-    <row r="635" ht="12.0" customHeight="1"/>
-    <row r="636" ht="12.0" customHeight="1"/>
-    <row r="637" ht="12.0" customHeight="1"/>
-    <row r="638" ht="12.0" customHeight="1"/>
-    <row r="639" ht="12.0" customHeight="1"/>
-    <row r="640" ht="12.0" customHeight="1"/>
-    <row r="641" ht="12.0" customHeight="1"/>
-    <row r="642" ht="12.0" customHeight="1"/>
-    <row r="643" ht="12.0" customHeight="1"/>
-    <row r="644" ht="12.0" customHeight="1"/>
-    <row r="645" ht="12.0" customHeight="1"/>
-    <row r="646" ht="12.0" customHeight="1"/>
-    <row r="647" ht="12.0" customHeight="1"/>
-    <row r="648" ht="12.0" customHeight="1"/>
-    <row r="649" ht="12.0" customHeight="1"/>
-    <row r="650" ht="12.0" customHeight="1"/>
-    <row r="651" ht="12.0" customHeight="1"/>
-    <row r="652" ht="12.0" customHeight="1"/>
-    <row r="653" ht="12.0" customHeight="1"/>
-    <row r="654" ht="12.0" customHeight="1"/>
-    <row r="655" ht="12.0" customHeight="1"/>
-    <row r="656" ht="12.0" customHeight="1"/>
-    <row r="657" ht="12.0" customHeight="1"/>
-    <row r="658" ht="12.0" customHeight="1"/>
-    <row r="659" ht="12.0" customHeight="1"/>
-    <row r="660" ht="12.0" customHeight="1"/>
-    <row r="661" ht="12.0" customHeight="1"/>
-    <row r="662" ht="12.0" customHeight="1"/>
-    <row r="663" ht="12.0" customHeight="1"/>
-    <row r="664" ht="12.0" customHeight="1"/>
-    <row r="665" ht="12.0" customHeight="1"/>
-    <row r="666" ht="12.0" customHeight="1"/>
-    <row r="667" ht="12.0" customHeight="1"/>
-    <row r="668" ht="12.0" customHeight="1"/>
-    <row r="669" ht="12.0" customHeight="1"/>
-    <row r="670" ht="12.0" customHeight="1"/>
-    <row r="671" ht="12.0" customHeight="1"/>
-    <row r="672" ht="12.0" customHeight="1"/>
-    <row r="673" ht="12.0" customHeight="1"/>
-    <row r="674" ht="12.0" customHeight="1"/>
-    <row r="675" ht="12.0" customHeight="1"/>
-    <row r="676" ht="12.0" customHeight="1"/>
-    <row r="677" ht="12.0" customHeight="1"/>
-    <row r="678" ht="12.0" customHeight="1"/>
-    <row r="679" ht="12.0" customHeight="1"/>
-    <row r="680" ht="12.0" customHeight="1"/>
-    <row r="681" ht="12.0" customHeight="1"/>
-    <row r="682" ht="12.0" customHeight="1"/>
-    <row r="683" ht="12.0" customHeight="1"/>
-    <row r="684" ht="12.0" customHeight="1"/>
-    <row r="685" ht="12.0" customHeight="1"/>
-    <row r="686" ht="12.0" customHeight="1"/>
-    <row r="687" ht="12.0" customHeight="1"/>
-    <row r="688" ht="12.0" customHeight="1"/>
-    <row r="689" ht="12.0" customHeight="1"/>
-    <row r="690" ht="12.0" customHeight="1"/>
-    <row r="691" ht="12.0" customHeight="1"/>
-    <row r="692" ht="12.0" customHeight="1"/>
-    <row r="693" ht="12.0" customHeight="1"/>
-    <row r="694" ht="12.0" customHeight="1"/>
-    <row r="695" ht="12.0" customHeight="1"/>
-    <row r="696" ht="12.0" customHeight="1"/>
-    <row r="697" ht="12.0" customHeight="1"/>
-    <row r="698" ht="12.0" customHeight="1"/>
-    <row r="699" ht="12.0" customHeight="1"/>
-    <row r="700" ht="12.0" customHeight="1"/>
-    <row r="701" ht="12.0" customHeight="1"/>
-    <row r="702" ht="12.0" customHeight="1"/>
-    <row r="703" ht="12.0" customHeight="1"/>
-    <row r="704" ht="12.0" customHeight="1"/>
-    <row r="705" ht="12.0" customHeight="1"/>
-    <row r="706" ht="12.0" customHeight="1"/>
-    <row r="707" ht="12.0" customHeight="1"/>
-    <row r="708" ht="12.0" customHeight="1"/>
-    <row r="709" ht="12.0" customHeight="1"/>
-    <row r="710" ht="12.0" customHeight="1"/>
-    <row r="711" ht="12.0" customHeight="1"/>
-    <row r="712" ht="12.0" customHeight="1"/>
-    <row r="713" ht="12.0" customHeight="1"/>
-    <row r="714" ht="12.0" customHeight="1"/>
-    <row r="715" ht="12.0" customHeight="1"/>
-    <row r="716" ht="12.0" customHeight="1"/>
-    <row r="717" ht="12.0" customHeight="1"/>
-    <row r="718" ht="12.0" customHeight="1"/>
-    <row r="719" ht="12.0" customHeight="1"/>
-    <row r="720" ht="12.0" customHeight="1"/>
-    <row r="721" ht="12.0" customHeight="1"/>
-    <row r="722" ht="12.0" customHeight="1"/>
-    <row r="723" ht="12.0" customHeight="1"/>
-    <row r="724" ht="12.0" customHeight="1"/>
-    <row r="725" ht="12.0" customHeight="1"/>
-    <row r="726" ht="12.0" customHeight="1"/>
-    <row r="727" ht="12.0" customHeight="1"/>
-    <row r="728" ht="12.0" customHeight="1"/>
-    <row r="729" ht="12.0" customHeight="1"/>
-    <row r="730" ht="12.0" customHeight="1"/>
-    <row r="731" ht="12.0" customHeight="1"/>
-    <row r="732" ht="12.0" customHeight="1"/>
-    <row r="733" ht="12.0" customHeight="1"/>
-    <row r="734" ht="12.0" customHeight="1"/>
-    <row r="735" ht="12.0" customHeight="1"/>
-    <row r="736" ht="12.0" customHeight="1"/>
-    <row r="737" ht="12.0" customHeight="1"/>
-    <row r="738" ht="12.0" customHeight="1"/>
-    <row r="739" ht="12.0" customHeight="1"/>
-    <row r="740" ht="12.0" customHeight="1"/>
-    <row r="741" ht="12.0" customHeight="1"/>
-    <row r="742" ht="12.0" customHeight="1"/>
-    <row r="743" ht="12.0" customHeight="1"/>
-    <row r="744" ht="12.0" customHeight="1"/>
-    <row r="745" ht="12.0" customHeight="1"/>
-    <row r="746" ht="12.0" customHeight="1"/>
-    <row r="747" ht="12.0" customHeight="1"/>
-    <row r="748" ht="12.0" customHeight="1"/>
-    <row r="749" ht="12.0" customHeight="1"/>
-    <row r="750" ht="12.0" customHeight="1"/>
-    <row r="751" ht="12.0" customHeight="1"/>
-    <row r="752" ht="12.0" customHeight="1"/>
-    <row r="753" ht="12.0" customHeight="1"/>
-    <row r="754" ht="12.0" customHeight="1"/>
-    <row r="755" ht="12.0" customHeight="1"/>
-    <row r="756" ht="12.0" customHeight="1"/>
-    <row r="757" ht="12.0" customHeight="1"/>
-    <row r="758" ht="12.0" customHeight="1"/>
-    <row r="759" ht="12.0" customHeight="1"/>
-    <row r="760" ht="12.0" customHeight="1"/>
-    <row r="761" ht="12.0" customHeight="1"/>
-    <row r="762" ht="12.0" customHeight="1"/>
-    <row r="763" ht="12.0" customHeight="1"/>
-    <row r="764" ht="12.0" customHeight="1"/>
-    <row r="765" ht="12.0" customHeight="1"/>
-    <row r="766" ht="12.0" customHeight="1"/>
-    <row r="767" ht="12.0" customHeight="1"/>
-    <row r="768" ht="12.0" customHeight="1"/>
-    <row r="769" ht="12.0" customHeight="1"/>
-    <row r="770" ht="12.0" customHeight="1"/>
-    <row r="771" ht="12.0" customHeight="1"/>
-    <row r="772" ht="12.0" customHeight="1"/>
-    <row r="773" ht="12.0" customHeight="1"/>
-    <row r="774" ht="12.0" customHeight="1"/>
-    <row r="775" ht="12.0" customHeight="1"/>
-    <row r="776" ht="12.0" customHeight="1"/>
-    <row r="777" ht="12.0" customHeight="1"/>
-    <row r="778" ht="12.0" customHeight="1"/>
-    <row r="779" ht="12.0" customHeight="1"/>
-    <row r="780" ht="12.0" customHeight="1"/>
-    <row r="781" ht="12.0" customHeight="1"/>
-    <row r="782" ht="12.0" customHeight="1"/>
-    <row r="783" ht="12.0" customHeight="1"/>
-    <row r="784" ht="12.0" customHeight="1"/>
-    <row r="785" ht="12.0" customHeight="1"/>
-    <row r="786" ht="12.0" customHeight="1"/>
-    <row r="787" ht="12.0" customHeight="1"/>
-    <row r="788" ht="12.0" customHeight="1"/>
-    <row r="789" ht="12.0" customHeight="1"/>
-    <row r="790" ht="12.0" customHeight="1"/>
-    <row r="791" ht="12.0" customHeight="1"/>
-    <row r="792" ht="12.0" customHeight="1"/>
-    <row r="793" ht="12.0" customHeight="1"/>
-    <row r="794" ht="12.0" customHeight="1"/>
-    <row r="795" ht="12.0" customHeight="1"/>
-    <row r="796" ht="12.0" customHeight="1"/>
-    <row r="797" ht="12.0" customHeight="1"/>
-    <row r="798" ht="12.0" customHeight="1"/>
-    <row r="799" ht="12.0" customHeight="1"/>
-    <row r="800" ht="12.0" customHeight="1"/>
-    <row r="801" ht="12.0" customHeight="1"/>
-    <row r="802" ht="12.0" customHeight="1"/>
-    <row r="803" ht="12.0" customHeight="1"/>
-    <row r="804" ht="12.0" customHeight="1"/>
-    <row r="805" ht="12.0" customHeight="1"/>
-    <row r="806" ht="12.0" customHeight="1"/>
-    <row r="807" ht="12.0" customHeight="1"/>
-    <row r="808" ht="12.0" customHeight="1"/>
-    <row r="809" ht="12.0" customHeight="1"/>
-    <row r="810" ht="12.0" customHeight="1"/>
-    <row r="811" ht="12.0" customHeight="1"/>
-    <row r="812" ht="12.0" customHeight="1"/>
-    <row r="813" ht="12.0" customHeight="1"/>
-    <row r="814" ht="12.0" customHeight="1"/>
-    <row r="815" ht="12.0" customHeight="1"/>
-    <row r="816" ht="12.0" customHeight="1"/>
-    <row r="817" ht="12.0" customHeight="1"/>
-    <row r="818" ht="12.0" customHeight="1"/>
-    <row r="819" ht="12.0" customHeight="1"/>
-    <row r="820" ht="12.0" customHeight="1"/>
-    <row r="821" ht="12.0" customHeight="1"/>
-    <row r="822" ht="12.0" customHeight="1"/>
-    <row r="823" ht="12.0" customHeight="1"/>
-    <row r="824" ht="12.0" customHeight="1"/>
-    <row r="825" ht="12.0" customHeight="1"/>
-    <row r="826" ht="12.0" customHeight="1"/>
-    <row r="827" ht="12.0" customHeight="1"/>
-    <row r="828" ht="12.0" customHeight="1"/>
-    <row r="829" ht="12.0" customHeight="1"/>
-    <row r="830" ht="12.0" customHeight="1"/>
-    <row r="831" ht="12.0" customHeight="1"/>
-    <row r="832" ht="12.0" customHeight="1"/>
-    <row r="833" ht="12.0" customHeight="1"/>
-    <row r="834" ht="12.0" customHeight="1"/>
-    <row r="835" ht="12.0" customHeight="1"/>
-    <row r="836" ht="12.0" customHeight="1"/>
-    <row r="837" ht="12.0" customHeight="1"/>
-    <row r="838" ht="12.0" customHeight="1"/>
-    <row r="839" ht="12.0" customHeight="1"/>
-    <row r="840" ht="12.0" customHeight="1"/>
-    <row r="841" ht="12.0" customHeight="1"/>
-    <row r="842" ht="12.0" customHeight="1"/>
-    <row r="843" ht="12.0" customHeight="1"/>
-    <row r="844" ht="12.0" customHeight="1"/>
-    <row r="845" ht="12.0" customHeight="1"/>
-    <row r="846" ht="12.0" customHeight="1"/>
-    <row r="847" ht="12.0" customHeight="1"/>
-    <row r="848" ht="12.0" customHeight="1"/>
-    <row r="849" ht="12.0" customHeight="1"/>
-    <row r="850" ht="12.0" customHeight="1"/>
-    <row r="851" ht="12.0" customHeight="1"/>
-    <row r="852" ht="12.0" customHeight="1"/>
-    <row r="853" ht="12.0" customHeight="1"/>
-    <row r="854" ht="12.0" customHeight="1"/>
-    <row r="855" ht="12.0" customHeight="1"/>
-    <row r="856" ht="12.0" customHeight="1"/>
-    <row r="857" ht="12.0" customHeight="1"/>
-    <row r="858" ht="12.0" customHeight="1"/>
-    <row r="859" ht="12.0" customHeight="1"/>
-    <row r="860" ht="12.0" customHeight="1"/>
-    <row r="861" ht="12.0" customHeight="1"/>
-    <row r="862" ht="12.0" customHeight="1"/>
-    <row r="863" ht="12.0" customHeight="1"/>
-    <row r="864" ht="12.0" customHeight="1"/>
-    <row r="865" ht="12.0" customHeight="1"/>
-    <row r="866" ht="12.0" customHeight="1"/>
-    <row r="867" ht="12.0" customHeight="1"/>
-    <row r="868" ht="12.0" customHeight="1"/>
-    <row r="869" ht="12.0" customHeight="1"/>
-    <row r="870" ht="12.0" customHeight="1"/>
-    <row r="871" ht="12.0" customHeight="1"/>
-    <row r="872" ht="12.0" customHeight="1"/>
-    <row r="873" ht="12.0" customHeight="1"/>
-    <row r="874" ht="12.0" customHeight="1"/>
-    <row r="875" ht="12.0" customHeight="1"/>
-    <row r="876" ht="12.0" customHeight="1"/>
-    <row r="877" ht="12.0" customHeight="1"/>
-    <row r="878" ht="12.0" customHeight="1"/>
-    <row r="879" ht="12.0" customHeight="1"/>
-    <row r="880" ht="12.0" customHeight="1"/>
-    <row r="881" ht="12.0" customHeight="1"/>
-    <row r="882" ht="12.0" customHeight="1"/>
-    <row r="883" ht="12.0" customHeight="1"/>
-    <row r="884" ht="12.0" customHeight="1"/>
-    <row r="885" ht="12.0" customHeight="1"/>
-    <row r="886" ht="12.0" customHeight="1"/>
-    <row r="887" ht="12.0" customHeight="1"/>
-    <row r="888" ht="12.0" customHeight="1"/>
-    <row r="889" ht="12.0" customHeight="1"/>
-    <row r="890" ht="12.0" customHeight="1"/>
-    <row r="891" ht="12.0" customHeight="1"/>
-    <row r="892" ht="12.0" customHeight="1"/>
-    <row r="893" ht="12.0" customHeight="1"/>
-    <row r="894" ht="12.0" customHeight="1"/>
-    <row r="895" ht="12.0" customHeight="1"/>
-    <row r="896" ht="12.0" customHeight="1"/>
-    <row r="897" ht="12.0" customHeight="1"/>
-    <row r="898" ht="12.0" customHeight="1"/>
-    <row r="899" ht="12.0" customHeight="1"/>
-    <row r="900" ht="12.0" customHeight="1"/>
-    <row r="901" ht="12.0" customHeight="1"/>
-    <row r="902" ht="12.0" customHeight="1"/>
-    <row r="903" ht="12.0" customHeight="1"/>
-    <row r="904" ht="12.0" customHeight="1"/>
-    <row r="905" ht="12.0" customHeight="1"/>
-    <row r="906" ht="12.0" customHeight="1"/>
-    <row r="907" ht="12.0" customHeight="1"/>
-    <row r="908" ht="12.0" customHeight="1"/>
-    <row r="909" ht="12.0" customHeight="1"/>
-    <row r="910" ht="12.0" customHeight="1"/>
-    <row r="911" ht="12.0" customHeight="1"/>
-    <row r="912" ht="12.0" customHeight="1"/>
-    <row r="913" ht="12.0" customHeight="1"/>
-    <row r="914" ht="12.0" customHeight="1"/>
-    <row r="915" ht="12.0" customHeight="1"/>
-    <row r="916" ht="12.0" customHeight="1"/>
-    <row r="917" ht="12.0" customHeight="1"/>
-    <row r="918" ht="12.0" customHeight="1"/>
-    <row r="919" ht="12.0" customHeight="1"/>
-    <row r="920" ht="12.0" customHeight="1"/>
-    <row r="921" ht="12.0" customHeight="1"/>
-    <row r="922" ht="12.0" customHeight="1"/>
-    <row r="923" ht="12.0" customHeight="1"/>
-    <row r="924" ht="12.0" customHeight="1"/>
-    <row r="925" ht="12.0" customHeight="1"/>
-    <row r="926" ht="12.0" customHeight="1"/>
-    <row r="927" ht="12.0" customHeight="1"/>
-    <row r="928" ht="12.0" customHeight="1"/>
-    <row r="929" ht="12.0" customHeight="1"/>
-    <row r="930" ht="12.0" customHeight="1"/>
-    <row r="931" ht="12.0" customHeight="1"/>
-    <row r="932" ht="12.0" customHeight="1"/>
-    <row r="933" ht="12.0" customHeight="1"/>
-    <row r="934" ht="12.0" customHeight="1"/>
-    <row r="935" ht="12.0" customHeight="1"/>
-    <row r="936" ht="12.0" customHeight="1"/>
-    <row r="937" ht="12.0" customHeight="1"/>
-    <row r="938" ht="12.0" customHeight="1"/>
-    <row r="939" ht="12.0" customHeight="1"/>
-    <row r="940" ht="12.0" customHeight="1"/>
-    <row r="941" ht="12.0" customHeight="1"/>
-    <row r="942" ht="12.0" customHeight="1"/>
-    <row r="943" ht="12.0" customHeight="1"/>
-    <row r="944" ht="12.0" customHeight="1"/>
-    <row r="945" ht="12.0" customHeight="1"/>
-    <row r="946" ht="12.0" customHeight="1"/>
-    <row r="947" ht="12.0" customHeight="1"/>
-    <row r="948" ht="12.0" customHeight="1"/>
-    <row r="949" ht="12.0" customHeight="1"/>
-    <row r="950" ht="12.0" customHeight="1"/>
-    <row r="951" ht="12.0" customHeight="1"/>
-    <row r="952" ht="12.0" customHeight="1"/>
-    <row r="953" ht="12.0" customHeight="1"/>
-    <row r="954" ht="12.0" customHeight="1"/>
-    <row r="955" ht="12.0" customHeight="1"/>
-    <row r="956" ht="12.0" customHeight="1"/>
-    <row r="957" ht="12.0" customHeight="1"/>
-    <row r="958" ht="12.0" customHeight="1"/>
-    <row r="959" ht="12.0" customHeight="1"/>
-    <row r="960" ht="12.0" customHeight="1"/>
-    <row r="961" ht="12.0" customHeight="1"/>
-    <row r="962" ht="12.0" customHeight="1"/>
-    <row r="963" ht="12.0" customHeight="1"/>
-    <row r="964" ht="12.0" customHeight="1"/>
-    <row r="965" ht="12.0" customHeight="1"/>
-    <row r="966" ht="12.0" customHeight="1"/>
-    <row r="967" ht="12.0" customHeight="1"/>
-    <row r="968" ht="12.0" customHeight="1"/>
-    <row r="969" ht="12.0" customHeight="1"/>
-    <row r="970" ht="12.0" customHeight="1"/>
-    <row r="971" ht="12.0" customHeight="1"/>
-    <row r="972" ht="12.0" customHeight="1"/>
-    <row r="973" ht="12.0" customHeight="1"/>
-    <row r="974" ht="12.0" customHeight="1"/>
-    <row r="975" ht="12.0" customHeight="1"/>
-    <row r="976" ht="12.0" customHeight="1"/>
-    <row r="977" ht="12.0" customHeight="1"/>
-    <row r="978" ht="12.0" customHeight="1"/>
-    <row r="979" ht="12.0" customHeight="1"/>
-    <row r="980" ht="12.0" customHeight="1"/>
-    <row r="981" ht="12.0" customHeight="1"/>
-    <row r="982" ht="12.0" customHeight="1"/>
-    <row r="983" ht="12.0" customHeight="1"/>
-    <row r="984" ht="12.0" customHeight="1"/>
-    <row r="985" ht="12.0" customHeight="1"/>
-    <row r="986" ht="12.0" customHeight="1"/>
-    <row r="987" ht="12.0" customHeight="1"/>
-    <row r="988" ht="12.0" customHeight="1"/>
-    <row r="989" ht="12.0" customHeight="1"/>
-    <row r="990" ht="12.0" customHeight="1"/>
-    <row r="991" ht="12.0" customHeight="1"/>
-    <row r="992" ht="12.0" customHeight="1"/>
-    <row r="993" ht="12.0" customHeight="1"/>
-    <row r="994" ht="12.0" customHeight="1"/>
-    <row r="995" ht="12.0" customHeight="1"/>
-    <row r="996" ht="12.0" customHeight="1"/>
-    <row r="997" ht="12.0" customHeight="1"/>
-    <row r="998" ht="12.0" customHeight="1"/>
-    <row r="999" ht="12.0" customHeight="1"/>
-    <row r="1000" ht="12.0" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -1777,160 +2928,160 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.57"/>
-    <col customWidth="1" min="2" max="2" width="17.86"/>
-    <col customWidth="1" min="3" max="3" width="26.71"/>
-    <col customWidth="1" min="4" max="4" width="18.0"/>
-    <col customWidth="1" min="5" max="5" width="18.29"/>
-    <col customWidth="1" min="6" max="6" width="17.71"/>
-    <col customWidth="1" min="7" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="15.38"/>
+    <col customWidth="1" min="2" max="2" width="15.63"/>
+    <col customWidth="1" min="3" max="3" width="23.38"/>
+    <col customWidth="1" min="4" max="4" width="15.75"/>
+    <col customWidth="1" min="5" max="5" width="16.0"/>
+    <col customWidth="1" min="6" max="6" width="15.5"/>
+    <col customWidth="1" min="7" max="25" width="7.63"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.0" customHeight="1">
-      <c r="A1" s="14" t="s">
+    <row r="1">
+      <c r="A1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="15"/>
-    </row>
-    <row r="2" ht="12.0" customHeight="1">
-      <c r="A2" t="s">
+      <c r="F1" s="13"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" ht="12.0" customHeight="1">
-      <c r="B3" t="s">
+    <row r="3">
+      <c r="B3" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" ht="12.0" customHeight="1">
-      <c r="B4" t="s">
+    <row r="4">
+      <c r="B4" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" ht="12.0" customHeight="1">
-      <c r="B5" t="s">
+    <row r="5">
+      <c r="B5" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="15" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" ht="12.0" customHeight="1">
-      <c r="B6" t="s">
+    <row r="6">
+      <c r="B6" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7" ht="12.0" customHeight="1">
-      <c r="B7" t="s">
+    <row r="7">
+      <c r="B7" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="8" ht="12.0" customHeight="1">
-      <c r="B8" t="s">
+    <row r="8">
+      <c r="B8" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="16">
         <v>-1.0E20</v>
       </c>
     </row>
-    <row r="9" ht="12.0" customHeight="1">
+    <row r="9">
       <c r="B9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="17" t="s">
         <v>48</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="20"/>
-    </row>
-    <row r="10" ht="12.0" customHeight="1">
+      <c r="F9" s="18"/>
+    </row>
+    <row r="10">
       <c r="B10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="17" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="20"/>
-    </row>
-    <row r="11" ht="12.0" customHeight="1">
-      <c r="B11" t="s">
+      <c r="F10" s="18"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" ht="12.0" customHeight="1">
-      <c r="B12" t="s">
+    <row r="12">
+      <c r="B12" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="15" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" ht="12.0" customHeight="1">
-      <c r="C13" s="17"/>
-    </row>
-    <row r="14" ht="12.0" customHeight="1">
+    <row r="13">
+      <c r="C13" s="15"/>
+    </row>
+    <row r="14">
       <c r="A14" s="5" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="15" ht="12.0" customHeight="1">
-      <c r="B15" t="s">
+    <row r="15">
+      <c r="B15" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" ht="12.0" customHeight="1">
-      <c r="B16" t="s">
+    <row r="16">
+      <c r="B16" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" ht="12.0" customHeight="1">
-      <c r="B17" t="s">
+    <row r="17">
+      <c r="B17" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="18" ht="12.0" customHeight="1">
-      <c r="B18" t="s">
+    <row r="18">
+      <c r="B18" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="5"/>
@@ -1938,58 +3089,58 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" ht="12.0" customHeight="1">
-      <c r="B19" t="s">
+    <row r="19">
+      <c r="B19" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="15" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="20" ht="12.0" customHeight="1">
-      <c r="B20" t="s">
+    <row r="20">
+      <c r="B20" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="16">
         <v>-127.0</v>
       </c>
     </row>
-    <row r="21" ht="12.0" customHeight="1">
+    <row r="21">
       <c r="B21" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="17" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22" ht="12.0" customHeight="1">
+    <row r="22">
       <c r="B22" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="17" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23" ht="12.0" customHeight="1">
-      <c r="B23" t="s">
+    <row r="23">
+      <c r="B23" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="24" ht="12.0" customHeight="1">
-      <c r="B24" t="s">
+    <row r="24">
+      <c r="B24" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="15" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25" ht="12.0" customHeight="1">
-      <c r="C25" s="17"/>
-    </row>
-    <row r="26" ht="12.0" customHeight="1">
+    <row r="25">
+      <c r="C25" s="15"/>
+    </row>
+    <row r="26">
       <c r="A26" s="4" t="s">
         <v>59</v>
       </c>
@@ -2017,14 +3168,13 @@
       <c r="W26" s="4"/>
       <c r="X26" s="4"/>
       <c r="Y26" s="4"/>
-      <c r="Z26" s="4"/>
-    </row>
-    <row r="27" ht="12.0" customHeight="1">
+    </row>
+    <row r="27">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D27" s="4"/>
@@ -2049,9 +3199,8 @@
       <c r="W27" s="4"/>
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
-      <c r="Z27" s="4"/>
-    </row>
-    <row r="28" ht="12.0" customHeight="1">
+    </row>
+    <row r="28">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>40</v>
@@ -2081,9 +3230,8 @@
       <c r="W28" s="4"/>
       <c r="X28" s="4"/>
       <c r="Y28" s="4"/>
-      <c r="Z28" s="4"/>
-    </row>
-    <row r="29" ht="12.0" customHeight="1">
+    </row>
+    <row r="29">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>29</v>
@@ -2113,9 +3261,8 @@
       <c r="W29" s="4"/>
       <c r="X29" s="4"/>
       <c r="Y29" s="4"/>
-      <c r="Z29" s="4"/>
-    </row>
-    <row r="30" ht="12.0" customHeight="1">
+    </row>
+    <row r="30">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>43</v>
@@ -2145,9 +3292,8 @@
       <c r="W30" s="4"/>
       <c r="X30" s="4"/>
       <c r="Y30" s="4"/>
-      <c r="Z30" s="4"/>
-    </row>
-    <row r="31" ht="12.0" customHeight="1">
+    </row>
+    <row r="31">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
         <v>44</v>
@@ -2177,14 +3323,13 @@
       <c r="W31" s="4"/>
       <c r="X31" s="4"/>
       <c r="Y31" s="4"/>
-      <c r="Z31" s="4"/>
-    </row>
-    <row r="32" ht="12.0" customHeight="1">
+    </row>
+    <row r="32">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="23">
+      <c r="C32" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D32" s="4"/>
@@ -2209,14 +3354,13 @@
       <c r="W32" s="4"/>
       <c r="X32" s="4"/>
       <c r="Y32" s="4"/>
-      <c r="Z32" s="4"/>
-    </row>
-    <row r="33" ht="12.0" customHeight="1">
+    </row>
+    <row r="33">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D33" s="4"/>
@@ -2241,14 +3385,13 @@
       <c r="W33" s="4"/>
       <c r="X33" s="4"/>
       <c r="Y33" s="4"/>
-      <c r="Z33" s="4"/>
-    </row>
-    <row r="34" ht="12.0" customHeight="1">
+    </row>
+    <row r="34">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D34" s="4"/>
@@ -2273,9 +3416,8 @@
       <c r="W34" s="4"/>
       <c r="X34" s="4"/>
       <c r="Y34" s="4"/>
-      <c r="Z34" s="4"/>
-    </row>
-    <row r="35" ht="12.0" customHeight="1">
+    </row>
+    <row r="35">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>51</v>
@@ -2305,9 +3447,8 @@
       <c r="W35" s="4"/>
       <c r="X35" s="4"/>
       <c r="Y35" s="4"/>
-      <c r="Z35" s="4"/>
-    </row>
-    <row r="36" ht="12.0" customHeight="1">
+    </row>
+    <row r="36">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>53</v>
@@ -2337,9 +3478,8 @@
       <c r="W36" s="4"/>
       <c r="X36" s="4"/>
       <c r="Y36" s="4"/>
-      <c r="Z36" s="4"/>
-    </row>
-    <row r="37" ht="12.0" customHeight="1">
+    </row>
+    <row r="37">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -2365,9 +3505,8 @@
       <c r="W37" s="4"/>
       <c r="X37" s="4"/>
       <c r="Y37" s="4"/>
-      <c r="Z37" s="4"/>
-    </row>
-    <row r="38" ht="12.0" customHeight="1">
+    </row>
+    <row r="38">
       <c r="A38" s="4" t="s">
         <v>64</v>
       </c>
@@ -2395,14 +3534,13 @@
       <c r="W38" s="4"/>
       <c r="X38" s="4"/>
       <c r="Y38" s="4"/>
-      <c r="Z38" s="4"/>
-    </row>
-    <row r="39" ht="12.0" customHeight="1">
+    </row>
+    <row r="39">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D39" s="4"/>
@@ -2427,9 +3565,8 @@
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
       <c r="Y39" s="4"/>
-      <c r="Z39" s="4"/>
-    </row>
-    <row r="40" ht="12.0" customHeight="1">
+    </row>
+    <row r="40">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
         <v>40</v>
@@ -2459,9 +3596,8 @@
       <c r="W40" s="4"/>
       <c r="X40" s="4"/>
       <c r="Y40" s="4"/>
-      <c r="Z40" s="4"/>
-    </row>
-    <row r="41" ht="12.0" customHeight="1">
+    </row>
+    <row r="41">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
         <v>29</v>
@@ -2491,9 +3627,8 @@
       <c r="W41" s="4"/>
       <c r="X41" s="4"/>
       <c r="Y41" s="4"/>
-      <c r="Z41" s="4"/>
-    </row>
-    <row r="42" ht="12.0" customHeight="1">
+    </row>
+    <row r="42">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>43</v>
@@ -2523,9 +3658,8 @@
       <c r="W42" s="4"/>
       <c r="X42" s="4"/>
       <c r="Y42" s="4"/>
-      <c r="Z42" s="4"/>
-    </row>
-    <row r="43" ht="12.0" customHeight="1">
+    </row>
+    <row r="43">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
         <v>44</v>
@@ -2555,14 +3689,13 @@
       <c r="W43" s="4"/>
       <c r="X43" s="4"/>
       <c r="Y43" s="4"/>
-      <c r="Z43" s="4"/>
-    </row>
-    <row r="44" ht="12.0" customHeight="1">
+    </row>
+    <row r="44">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="23">
+      <c r="C44" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D44" s="4"/>
@@ -2587,14 +3720,13 @@
       <c r="W44" s="4"/>
       <c r="X44" s="4"/>
       <c r="Y44" s="4"/>
-      <c r="Z44" s="4"/>
-    </row>
-    <row r="45" ht="12.0" customHeight="1">
+    </row>
+    <row r="45">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="24" t="s">
+      <c r="C45" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D45" s="4"/>
@@ -2619,14 +3751,13 @@
       <c r="W45" s="4"/>
       <c r="X45" s="4"/>
       <c r="Y45" s="4"/>
-      <c r="Z45" s="4"/>
-    </row>
-    <row r="46" ht="12.0" customHeight="1">
+    </row>
+    <row r="46">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="24" t="s">
+      <c r="C46" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D46" s="4"/>
@@ -2651,9 +3782,8 @@
       <c r="W46" s="4"/>
       <c r="X46" s="4"/>
       <c r="Y46" s="4"/>
-      <c r="Z46" s="4"/>
-    </row>
-    <row r="47" ht="12.0" customHeight="1">
+    </row>
+    <row r="47">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
         <v>51</v>
@@ -2683,9 +3813,8 @@
       <c r="W47" s="4"/>
       <c r="X47" s="4"/>
       <c r="Y47" s="4"/>
-      <c r="Z47" s="4"/>
-    </row>
-    <row r="48" ht="12.0" customHeight="1">
+    </row>
+    <row r="48">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
         <v>53</v>
@@ -2715,9 +3844,8 @@
       <c r="W48" s="4"/>
       <c r="X48" s="4"/>
       <c r="Y48" s="4"/>
-      <c r="Z48" s="4"/>
-    </row>
-    <row r="49" ht="12.0" customHeight="1">
+    </row>
+    <row r="49">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -2743,10 +3871,9 @@
       <c r="W49" s="4"/>
       <c r="X49" s="4"/>
       <c r="Y49" s="4"/>
-      <c r="Z49" s="4"/>
-    </row>
-    <row r="50" ht="12.0" customHeight="1">
-      <c r="A50" s="25" t="s">
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="s">
         <v>67</v>
       </c>
       <c r="B50" s="4"/>
@@ -2773,14 +3900,13 @@
       <c r="W50" s="4"/>
       <c r="X50" s="4"/>
       <c r="Y50" s="4"/>
-      <c r="Z50" s="4"/>
-    </row>
-    <row r="51" ht="12.0" customHeight="1">
+    </row>
+    <row r="51">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C51" s="22" t="s">
+      <c r="C51" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D51" s="4"/>
@@ -2805,9 +3931,8 @@
       <c r="W51" s="4"/>
       <c r="X51" s="4"/>
       <c r="Y51" s="4"/>
-      <c r="Z51" s="4"/>
-    </row>
-    <row r="52" ht="12.0" customHeight="1">
+    </row>
+    <row r="52">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
         <v>40</v>
@@ -2837,9 +3962,8 @@
       <c r="W52" s="4"/>
       <c r="X52" s="4"/>
       <c r="Y52" s="4"/>
-      <c r="Z52" s="4"/>
-    </row>
-    <row r="53" ht="12.0" customHeight="1">
+    </row>
+    <row r="53">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
         <v>29</v>
@@ -2869,14 +3993,13 @@
       <c r="W53" s="4"/>
       <c r="X53" s="4"/>
       <c r="Y53" s="4"/>
-      <c r="Z53" s="4"/>
-    </row>
-    <row r="54" ht="12.0" customHeight="1">
+    </row>
+    <row r="54">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C54" s="25" t="s">
+      <c r="C54" s="4" t="s">
         <v>67</v>
       </c>
       <c r="D54" s="4"/>
@@ -2901,14 +4024,13 @@
       <c r="W54" s="4"/>
       <c r="X54" s="4"/>
       <c r="Y54" s="4"/>
-      <c r="Z54" s="4"/>
-    </row>
-    <row r="55" ht="12.0" customHeight="1">
+    </row>
+    <row r="55">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="22" t="s">
+      <c r="C55" s="19" t="s">
         <v>69</v>
       </c>
       <c r="D55" s="4"/>
@@ -2933,14 +4055,13 @@
       <c r="W55" s="4"/>
       <c r="X55" s="4"/>
       <c r="Y55" s="4"/>
-      <c r="Z55" s="4"/>
-    </row>
-    <row r="56" ht="12.0" customHeight="1">
+    </row>
+    <row r="56">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C56" s="23">
+      <c r="C56" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D56" s="4"/>
@@ -2965,14 +4086,13 @@
       <c r="W56" s="4"/>
       <c r="X56" s="4"/>
       <c r="Y56" s="4"/>
-      <c r="Z56" s="4"/>
-    </row>
-    <row r="57" ht="12.0" customHeight="1">
+    </row>
+    <row r="57">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C57" s="24" t="s">
+      <c r="C57" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D57" s="4"/>
@@ -2997,14 +4117,13 @@
       <c r="W57" s="4"/>
       <c r="X57" s="4"/>
       <c r="Y57" s="4"/>
-      <c r="Z57" s="4"/>
-    </row>
-    <row r="58" ht="12.0" customHeight="1">
+    </row>
+    <row r="58">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="C58" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D58" s="4"/>
@@ -3029,9 +4148,8 @@
       <c r="W58" s="4"/>
       <c r="X58" s="4"/>
       <c r="Y58" s="4"/>
-      <c r="Z58" s="4"/>
-    </row>
-    <row r="59" ht="12.0" customHeight="1">
+    </row>
+    <row r="59">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
         <v>51</v>
@@ -3061,9 +4179,8 @@
       <c r="W59" s="4"/>
       <c r="X59" s="4"/>
       <c r="Y59" s="4"/>
-      <c r="Z59" s="4"/>
-    </row>
-    <row r="60" ht="12.0" customHeight="1">
+    </row>
+    <row r="60">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
         <v>53</v>
@@ -3093,9 +4210,8 @@
       <c r="W60" s="4"/>
       <c r="X60" s="4"/>
       <c r="Y60" s="4"/>
-      <c r="Z60" s="4"/>
-    </row>
-    <row r="61" ht="12.0" customHeight="1">
+    </row>
+    <row r="61">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -3121,10 +4237,9 @@
       <c r="W61" s="4"/>
       <c r="X61" s="4"/>
       <c r="Y61" s="4"/>
-      <c r="Z61" s="4"/>
-    </row>
-    <row r="62" ht="12.0" customHeight="1">
-      <c r="A62" s="20" t="s">
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="s">
         <v>70</v>
       </c>
       <c r="B62" s="4"/>
@@ -3151,14 +4266,13 @@
       <c r="W62" s="4"/>
       <c r="X62" s="4"/>
       <c r="Y62" s="4"/>
-      <c r="Z62" s="4"/>
-    </row>
-    <row r="63" ht="12.0" customHeight="1">
+    </row>
+    <row r="63">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C63" s="22" t="s">
+      <c r="C63" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D63" s="4"/>
@@ -3183,9 +4297,8 @@
       <c r="W63" s="4"/>
       <c r="X63" s="4"/>
       <c r="Y63" s="4"/>
-      <c r="Z63" s="4"/>
-    </row>
-    <row r="64" ht="12.0" customHeight="1">
+    </row>
+    <row r="64">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
         <v>40</v>
@@ -3215,14 +4328,13 @@
       <c r="W64" s="4"/>
       <c r="X64" s="4"/>
       <c r="Y64" s="4"/>
-      <c r="Z64" s="4"/>
-    </row>
-    <row r="65" ht="12.0" customHeight="1">
+    </row>
+    <row r="65">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C65" s="26" t="s">
+      <c r="C65" s="3" t="s">
         <v>68</v>
       </c>
       <c r="D65" s="4"/>
@@ -3247,9 +4359,8 @@
       <c r="W65" s="4"/>
       <c r="X65" s="4"/>
       <c r="Y65" s="4"/>
-      <c r="Z65" s="4"/>
-    </row>
-    <row r="66" ht="12.0" customHeight="1">
+    </row>
+    <row r="66">
       <c r="A66" s="4"/>
       <c r="B66" s="4" t="s">
         <v>43</v>
@@ -3279,21 +4390,20 @@
       <c r="W66" s="4"/>
       <c r="X66" s="4"/>
       <c r="Y66" s="4"/>
-      <c r="Z66" s="4"/>
-    </row>
-    <row r="67" ht="12.0" customHeight="1">
+    </row>
+    <row r="67">
       <c r="A67" s="4"/>
       <c r="B67" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C67" s="22" t="s">
+      <c r="C67" s="19" t="s">
         <v>71</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
       <c r="G67" s="4"/>
-      <c r="H67" s="25"/>
+      <c r="H67" s="4"/>
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
@@ -3311,14 +4421,13 @@
       <c r="W67" s="4"/>
       <c r="X67" s="4"/>
       <c r="Y67" s="4"/>
-      <c r="Z67" s="4"/>
-    </row>
-    <row r="68" ht="12.0" customHeight="1">
+    </row>
+    <row r="68">
       <c r="A68" s="4"/>
       <c r="B68" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C68" s="23">
+      <c r="C68" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D68" s="4"/>
@@ -3327,7 +4436,7 @@
       <c r="G68" s="4"/>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
-      <c r="J68" s="25"/>
+      <c r="J68" s="4"/>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
@@ -3343,14 +4452,13 @@
       <c r="W68" s="4"/>
       <c r="X68" s="4"/>
       <c r="Y68" s="4"/>
-      <c r="Z68" s="4"/>
-    </row>
-    <row r="69" ht="12.0" customHeight="1">
+    </row>
+    <row r="69">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C69" s="24" t="s">
+      <c r="C69" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D69" s="4"/>
@@ -3359,7 +4467,7 @@
       <c r="G69" s="4"/>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
-      <c r="J69" s="25"/>
+      <c r="J69" s="4"/>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
@@ -3375,14 +4483,13 @@
       <c r="W69" s="4"/>
       <c r="X69" s="4"/>
       <c r="Y69" s="4"/>
-      <c r="Z69" s="4"/>
-    </row>
-    <row r="70" ht="12.0" customHeight="1">
+    </row>
+    <row r="70">
       <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C70" s="24" t="s">
+      <c r="C70" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D70" s="4"/>
@@ -3407,9 +4514,8 @@
       <c r="W70" s="4"/>
       <c r="X70" s="4"/>
       <c r="Y70" s="4"/>
-      <c r="Z70" s="4"/>
-    </row>
-    <row r="71" ht="12.0" customHeight="1">
+    </row>
+    <row r="71">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
         <v>51</v>
@@ -3439,9 +4545,8 @@
       <c r="W71" s="4"/>
       <c r="X71" s="4"/>
       <c r="Y71" s="4"/>
-      <c r="Z71" s="4"/>
-    </row>
-    <row r="72" ht="12.0" customHeight="1">
+    </row>
+    <row r="72">
       <c r="A72" s="4"/>
       <c r="B72" s="4" t="s">
         <v>53</v>
@@ -3455,7 +4560,7 @@
       <c r="G72" s="4"/>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
-      <c r="J72" s="25"/>
+      <c r="J72" s="4"/>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
@@ -3471,9 +4576,8 @@
       <c r="W72" s="4"/>
       <c r="X72" s="4"/>
       <c r="Y72" s="4"/>
-      <c r="Z72" s="4"/>
-    </row>
-    <row r="73" ht="12.0" customHeight="1">
+    </row>
+    <row r="73">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -3483,7 +4587,7 @@
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
-      <c r="J73" s="25"/>
+      <c r="J73" s="4"/>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
@@ -3499,9 +4603,8 @@
       <c r="W73" s="4"/>
       <c r="X73" s="4"/>
       <c r="Y73" s="4"/>
-      <c r="Z73" s="4"/>
-    </row>
-    <row r="74" ht="12.0" customHeight="1">
+    </row>
+    <row r="74">
       <c r="A74" s="4" t="s">
         <v>72</v>
       </c>
@@ -3513,7 +4616,7 @@
       <c r="G74" s="4"/>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
-      <c r="J74" s="25"/>
+      <c r="J74" s="4"/>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
@@ -3529,14 +4632,13 @@
       <c r="W74" s="4"/>
       <c r="X74" s="4"/>
       <c r="Y74" s="4"/>
-      <c r="Z74" s="4"/>
-    </row>
-    <row r="75" ht="12.0" customHeight="1">
+    </row>
+    <row r="75">
       <c r="A75" s="4"/>
       <c r="B75" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C75" s="22" t="s">
+      <c r="C75" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D75" s="4"/>
@@ -3561,9 +4663,8 @@
       <c r="W75" s="4"/>
       <c r="X75" s="4"/>
       <c r="Y75" s="4"/>
-      <c r="Z75" s="4"/>
-    </row>
-    <row r="76" ht="12.0" customHeight="1">
+    </row>
+    <row r="76">
       <c r="A76" s="4"/>
       <c r="B76" s="4" t="s">
         <v>40</v>
@@ -3593,14 +4694,13 @@
       <c r="W76" s="4"/>
       <c r="X76" s="4"/>
       <c r="Y76" s="4"/>
-      <c r="Z76" s="4"/>
-    </row>
-    <row r="77" ht="12.0" customHeight="1">
+    </row>
+    <row r="77">
       <c r="A77" s="4"/>
       <c r="B77" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C77" s="22">
+      <c r="C77" s="19">
         <v>1.0</v>
       </c>
       <c r="D77" s="4"/>
@@ -3625,9 +4725,8 @@
       <c r="W77" s="4"/>
       <c r="X77" s="4"/>
       <c r="Y77" s="4"/>
-      <c r="Z77" s="4"/>
-    </row>
-    <row r="78" ht="12.0" customHeight="1">
+    </row>
+    <row r="78">
       <c r="A78" s="4"/>
       <c r="B78" s="4" t="s">
         <v>43</v>
@@ -3655,14 +4754,13 @@
       <c r="W78" s="4"/>
       <c r="X78" s="4"/>
       <c r="Y78" s="4"/>
-      <c r="Z78" s="4"/>
-    </row>
-    <row r="79" ht="12.0" customHeight="1">
+    </row>
+    <row r="79">
       <c r="A79" s="4"/>
       <c r="B79" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C79" s="27" t="s">
+      <c r="C79" s="22" t="s">
         <v>73</v>
       </c>
       <c r="D79" s="4"/>
@@ -3687,14 +4785,13 @@
       <c r="W79" s="4"/>
       <c r="X79" s="4"/>
       <c r="Y79" s="4"/>
-      <c r="Z79" s="4"/>
-    </row>
-    <row r="80" ht="12.0" customHeight="1">
+    </row>
+    <row r="80">
       <c r="A80" s="4"/>
       <c r="B80" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C80" s="23">
+      <c r="C80" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D80" s="4"/>
@@ -3719,14 +4816,13 @@
       <c r="W80" s="4"/>
       <c r="X80" s="4"/>
       <c r="Y80" s="4"/>
-      <c r="Z80" s="4"/>
-    </row>
-    <row r="81" ht="12.0" customHeight="1">
+    </row>
+    <row r="81">
       <c r="A81" s="4"/>
       <c r="B81" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C81" s="24" t="s">
+      <c r="C81" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D81" s="4"/>
@@ -3751,14 +4847,13 @@
       <c r="W81" s="4"/>
       <c r="X81" s="4"/>
       <c r="Y81" s="4"/>
-      <c r="Z81" s="4"/>
-    </row>
-    <row r="82" ht="12.0" customHeight="1">
+    </row>
+    <row r="82">
       <c r="A82" s="4"/>
       <c r="B82" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C82" s="24" t="s">
+      <c r="C82" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D82" s="4"/>
@@ -3783,14 +4878,13 @@
       <c r="W82" s="4"/>
       <c r="X82" s="4"/>
       <c r="Y82" s="4"/>
-      <c r="Z82" s="4"/>
-    </row>
-    <row r="83" ht="12.0" customHeight="1">
+    </row>
+    <row r="83">
       <c r="A83" s="4"/>
       <c r="B83" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C83" s="28" t="s">
+      <c r="C83" s="19" t="s">
         <v>74</v>
       </c>
       <c r="D83" s="4"/>
@@ -3815,9 +4909,8 @@
       <c r="W83" s="4"/>
       <c r="X83" s="4"/>
       <c r="Y83" s="4"/>
-      <c r="Z83" s="4"/>
-    </row>
-    <row r="84" ht="12.0" customHeight="1">
+    </row>
+    <row r="84">
       <c r="A84" s="4"/>
       <c r="B84" s="4" t="s">
         <v>53</v>
@@ -3847,9 +4940,8 @@
       <c r="W84" s="4"/>
       <c r="X84" s="4"/>
       <c r="Y84" s="4"/>
-      <c r="Z84" s="4"/>
-    </row>
-    <row r="85" ht="12.0" customHeight="1">
+    </row>
+    <row r="85">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -3875,10 +4967,9 @@
       <c r="W85" s="4"/>
       <c r="X85" s="4"/>
       <c r="Y85" s="4"/>
-      <c r="Z85" s="4"/>
-    </row>
-    <row r="86" ht="12.0" customHeight="1">
-      <c r="A86" s="25" t="s">
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="s">
         <v>75</v>
       </c>
       <c r="B86" s="4"/>
@@ -3905,14 +4996,13 @@
       <c r="W86" s="4"/>
       <c r="X86" s="4"/>
       <c r="Y86" s="4"/>
-      <c r="Z86" s="4"/>
-    </row>
-    <row r="87" ht="12.0" customHeight="1">
+    </row>
+    <row r="87">
       <c r="A87" s="4"/>
       <c r="B87" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C87" s="22" t="s">
+      <c r="C87" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D87" s="4"/>
@@ -3937,14 +5027,13 @@
       <c r="W87" s="4"/>
       <c r="X87" s="4"/>
       <c r="Y87" s="4"/>
-      <c r="Z87" s="4"/>
-    </row>
-    <row r="88" ht="12.0" customHeight="1">
+    </row>
+    <row r="88">
       <c r="A88" s="4"/>
       <c r="B88" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C88" s="26" t="s">
+      <c r="C88" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D88" s="4"/>
@@ -3969,14 +5058,13 @@
       <c r="W88" s="4"/>
       <c r="X88" s="4"/>
       <c r="Y88" s="4"/>
-      <c r="Z88" s="4"/>
-    </row>
-    <row r="89" ht="12.0" customHeight="1">
+    </row>
+    <row r="89">
       <c r="A89" s="4"/>
       <c r="B89" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C89" s="28" t="s">
+      <c r="C89" s="19" t="s">
         <v>61</v>
       </c>
       <c r="D89" s="4"/>
@@ -4001,9 +5089,8 @@
       <c r="W89" s="4"/>
       <c r="X89" s="4"/>
       <c r="Y89" s="4"/>
-      <c r="Z89" s="4"/>
-    </row>
-    <row r="90" ht="12.0" customHeight="1">
+    </row>
+    <row r="90">
       <c r="A90" s="4"/>
       <c r="B90" s="4" t="s">
         <v>43</v>
@@ -4031,14 +5118,13 @@
       <c r="W90" s="4"/>
       <c r="X90" s="4"/>
       <c r="Y90" s="4"/>
-      <c r="Z90" s="4"/>
-    </row>
-    <row r="91" ht="12.0" customHeight="1">
+    </row>
+    <row r="91">
       <c r="A91" s="4"/>
       <c r="B91" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C91" s="22" t="s">
+      <c r="C91" s="19" t="s">
         <v>76</v>
       </c>
       <c r="D91" s="4"/>
@@ -4063,14 +5149,13 @@
       <c r="W91" s="4"/>
       <c r="X91" s="4"/>
       <c r="Y91" s="4"/>
-      <c r="Z91" s="4"/>
-    </row>
-    <row r="92" ht="12.0" customHeight="1">
+    </row>
+    <row r="92">
       <c r="A92" s="4"/>
       <c r="B92" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C92" s="23">
+      <c r="C92" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D92" s="4"/>
@@ -4095,14 +5180,13 @@
       <c r="W92" s="4"/>
       <c r="X92" s="4"/>
       <c r="Y92" s="4"/>
-      <c r="Z92" s="4"/>
-    </row>
-    <row r="93" ht="12.0" customHeight="1">
+    </row>
+    <row r="93">
       <c r="A93" s="4"/>
       <c r="B93" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C93" s="24" t="s">
+      <c r="C93" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D93" s="4"/>
@@ -4127,14 +5211,13 @@
       <c r="W93" s="4"/>
       <c r="X93" s="4"/>
       <c r="Y93" s="4"/>
-      <c r="Z93" s="4"/>
-    </row>
-    <row r="94" ht="12.0" customHeight="1">
+    </row>
+    <row r="94">
       <c r="A94" s="4"/>
       <c r="B94" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C94" s="24" t="s">
+      <c r="C94" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D94" s="4"/>
@@ -4159,14 +5242,13 @@
       <c r="W94" s="4"/>
       <c r="X94" s="4"/>
       <c r="Y94" s="4"/>
-      <c r="Z94" s="4"/>
-    </row>
-    <row r="95" ht="12.0" customHeight="1">
+    </row>
+    <row r="95">
       <c r="A95" s="4"/>
       <c r="B95" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C95" s="28" t="s">
+      <c r="C95" s="19" t="s">
         <v>77</v>
       </c>
       <c r="D95" s="4"/>
@@ -4191,14 +5273,13 @@
       <c r="W95" s="4"/>
       <c r="X95" s="4"/>
       <c r="Y95" s="4"/>
-      <c r="Z95" s="4"/>
-    </row>
-    <row r="96" ht="12.0" customHeight="1">
+    </row>
+    <row r="96">
       <c r="A96" s="4"/>
       <c r="B96" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C96" s="26" t="s">
+      <c r="C96" s="3" t="s">
         <v>54</v>
       </c>
       <c r="D96" s="4"/>
@@ -4223,9 +5304,8 @@
       <c r="W96" s="4"/>
       <c r="X96" s="4"/>
       <c r="Y96" s="4"/>
-      <c r="Z96" s="4"/>
-    </row>
-    <row r="97" ht="12.0" customHeight="1">
+    </row>
+    <row r="97">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -4251,10 +5331,9 @@
       <c r="W97" s="4"/>
       <c r="X97" s="4"/>
       <c r="Y97" s="4"/>
-      <c r="Z97" s="4"/>
-    </row>
-    <row r="98" ht="12.0" customHeight="1">
-      <c r="A98" s="20" t="s">
+    </row>
+    <row r="98">
+      <c r="A98" s="18" t="s">
         <v>78</v>
       </c>
       <c r="B98" s="4"/>
@@ -4281,14 +5360,13 @@
       <c r="W98" s="4"/>
       <c r="X98" s="4"/>
       <c r="Y98" s="4"/>
-      <c r="Z98" s="4"/>
-    </row>
-    <row r="99" ht="12.0" customHeight="1">
+    </row>
+    <row r="99">
       <c r="A99" s="4"/>
       <c r="B99" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C99" s="28" t="s">
+      <c r="C99" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D99" s="4"/>
@@ -4313,14 +5391,13 @@
       <c r="W99" s="4"/>
       <c r="X99" s="4"/>
       <c r="Y99" s="4"/>
-      <c r="Z99" s="4"/>
-    </row>
-    <row r="100" ht="12.0" customHeight="1">
+    </row>
+    <row r="100">
       <c r="A100" s="4"/>
       <c r="B100" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C100" s="26" t="s">
+      <c r="C100" s="3" t="s">
         <v>60</v>
       </c>
       <c r="D100" s="4"/>
@@ -4345,14 +5422,13 @@
       <c r="W100" s="4"/>
       <c r="X100" s="4"/>
       <c r="Y100" s="4"/>
-      <c r="Z100" s="4"/>
-    </row>
-    <row r="101" ht="12.0" customHeight="1">
+    </row>
+    <row r="101">
       <c r="A101" s="4"/>
       <c r="B101" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C101" s="22" t="s">
+      <c r="C101" s="19" t="s">
         <v>79</v>
       </c>
       <c r="D101" s="4"/>
@@ -4377,15 +5453,14 @@
       <c r="W101" s="4"/>
       <c r="X101" s="4"/>
       <c r="Y101" s="4"/>
-      <c r="Z101" s="4"/>
-    </row>
-    <row r="102" ht="12.0" customHeight="1">
+    </row>
+    <row r="102">
       <c r="A102" s="4"/>
       <c r="B102" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C102" s="26"/>
-      <c r="D102" s="20" t="s">
+      <c r="C102" s="3"/>
+      <c r="D102" s="18" t="s">
         <v>78</v>
       </c>
       <c r="E102" s="4"/>
@@ -4409,14 +5484,13 @@
       <c r="W102" s="4"/>
       <c r="X102" s="4"/>
       <c r="Y102" s="4"/>
-      <c r="Z102" s="4"/>
-    </row>
-    <row r="103" ht="12.0" customHeight="1">
+    </row>
+    <row r="103">
       <c r="A103" s="4"/>
       <c r="B103" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C103" s="28" t="s">
+      <c r="C103" s="19" t="s">
         <v>80</v>
       </c>
       <c r="D103" s="4"/>
@@ -4441,14 +5515,13 @@
       <c r="W103" s="4"/>
       <c r="X103" s="4"/>
       <c r="Y103" s="4"/>
-      <c r="Z103" s="4"/>
-    </row>
-    <row r="104" ht="12.0" customHeight="1">
+    </row>
+    <row r="104">
       <c r="A104" s="4"/>
       <c r="B104" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C104" s="23">
+      <c r="C104" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D104" s="4"/>
@@ -4473,14 +5546,13 @@
       <c r="W104" s="4"/>
       <c r="X104" s="4"/>
       <c r="Y104" s="4"/>
-      <c r="Z104" s="4"/>
-    </row>
-    <row r="105" ht="12.0" customHeight="1">
+    </row>
+    <row r="105">
       <c r="A105" s="4"/>
       <c r="B105" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C105" s="24" t="s">
+      <c r="C105" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D105" s="4"/>
@@ -4505,14 +5577,13 @@
       <c r="W105" s="4"/>
       <c r="X105" s="4"/>
       <c r="Y105" s="4"/>
-      <c r="Z105" s="4"/>
-    </row>
-    <row r="106" ht="12.0" customHeight="1">
+    </row>
+    <row r="106">
       <c r="A106" s="4"/>
       <c r="B106" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C106" s="24" t="s">
+      <c r="C106" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D106" s="4"/>
@@ -4537,9 +5608,8 @@
       <c r="W106" s="4"/>
       <c r="X106" s="4"/>
       <c r="Y106" s="4"/>
-      <c r="Z106" s="4"/>
-    </row>
-    <row r="107" ht="12.0" customHeight="1">
+    </row>
+    <row r="107">
       <c r="A107" s="4"/>
       <c r="B107" s="4" t="s">
         <v>51</v>
@@ -4569,9 +5639,8 @@
       <c r="W107" s="4"/>
       <c r="X107" s="4"/>
       <c r="Y107" s="4"/>
-      <c r="Z107" s="4"/>
-    </row>
-    <row r="108" ht="12.0" customHeight="1">
+    </row>
+    <row r="108">
       <c r="A108" s="4"/>
       <c r="B108" s="4" t="s">
         <v>53</v>
@@ -4601,9 +5670,8 @@
       <c r="W108" s="4"/>
       <c r="X108" s="4"/>
       <c r="Y108" s="4"/>
-      <c r="Z108" s="4"/>
-    </row>
-    <row r="109" ht="12.0" customHeight="1">
+    </row>
+    <row r="109">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -4629,10 +5697,9 @@
       <c r="W109" s="4"/>
       <c r="X109" s="4"/>
       <c r="Y109" s="4"/>
-      <c r="Z109" s="4"/>
-    </row>
-    <row r="110" ht="12.0" customHeight="1">
-      <c r="A110" s="20" t="s">
+    </row>
+    <row r="110">
+      <c r="A110" s="23" t="s">
         <v>81</v>
       </c>
       <c r="B110" s="4"/>
@@ -4659,14 +5726,13 @@
       <c r="W110" s="4"/>
       <c r="X110" s="4"/>
       <c r="Y110" s="4"/>
-      <c r="Z110" s="4"/>
-    </row>
-    <row r="111" ht="12.0" customHeight="1">
+    </row>
+    <row r="111">
       <c r="A111" s="4"/>
       <c r="B111" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C111" s="28" t="s">
+      <c r="C111" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D111" s="4"/>
@@ -4691,9 +5757,8 @@
       <c r="W111" s="4"/>
       <c r="X111" s="4"/>
       <c r="Y111" s="4"/>
-      <c r="Z111" s="4"/>
-    </row>
-    <row r="112" ht="12.0" customHeight="1">
+    </row>
+    <row r="112">
       <c r="A112" s="4"/>
       <c r="B112" s="4" t="s">
         <v>40</v>
@@ -4723,14 +5788,13 @@
       <c r="W112" s="4"/>
       <c r="X112" s="4"/>
       <c r="Y112" s="4"/>
-      <c r="Z112" s="4"/>
-    </row>
-    <row r="113" ht="12.0" customHeight="1">
+    </row>
+    <row r="113">
       <c r="A113" s="4"/>
       <c r="B113" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C113" s="28" t="s">
+      <c r="C113" s="19" t="s">
         <v>61</v>
       </c>
       <c r="D113" s="4"/>
@@ -4755,9 +5819,8 @@
       <c r="W113" s="4"/>
       <c r="X113" s="4"/>
       <c r="Y113" s="4"/>
-      <c r="Z113" s="4"/>
-    </row>
-    <row r="114" ht="12.0" customHeight="1">
+    </row>
+    <row r="114">
       <c r="A114" s="4"/>
       <c r="B114" s="4" t="s">
         <v>43</v>
@@ -4785,14 +5848,13 @@
       <c r="W114" s="4"/>
       <c r="X114" s="4"/>
       <c r="Y114" s="4"/>
-      <c r="Z114" s="4"/>
-    </row>
-    <row r="115" ht="12.0" customHeight="1">
+    </row>
+    <row r="115">
       <c r="A115" s="4"/>
       <c r="B115" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C115" s="28" t="s">
+      <c r="C115" s="19" t="s">
         <v>82</v>
       </c>
       <c r="D115" s="4"/>
@@ -4817,14 +5879,13 @@
       <c r="W115" s="4"/>
       <c r="X115" s="4"/>
       <c r="Y115" s="4"/>
-      <c r="Z115" s="4"/>
-    </row>
-    <row r="116" ht="12.0" customHeight="1">
+    </row>
+    <row r="116">
       <c r="A116" s="4"/>
       <c r="B116" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C116" s="23">
+      <c r="C116" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D116" s="4"/>
@@ -4849,14 +5910,13 @@
       <c r="W116" s="4"/>
       <c r="X116" s="4"/>
       <c r="Y116" s="4"/>
-      <c r="Z116" s="4"/>
-    </row>
-    <row r="117" ht="12.0" customHeight="1">
+    </row>
+    <row r="117">
       <c r="A117" s="4"/>
       <c r="B117" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C117" s="24" t="s">
+      <c r="C117" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D117" s="4"/>
@@ -4881,14 +5941,13 @@
       <c r="W117" s="4"/>
       <c r="X117" s="4"/>
       <c r="Y117" s="4"/>
-      <c r="Z117" s="4"/>
-    </row>
-    <row r="118" ht="12.0" customHeight="1">
+    </row>
+    <row r="118">
       <c r="A118" s="4"/>
       <c r="B118" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C118" s="24" t="s">
+      <c r="C118" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D118" s="4"/>
@@ -4913,9 +5972,8 @@
       <c r="W118" s="4"/>
       <c r="X118" s="4"/>
       <c r="Y118" s="4"/>
-      <c r="Z118" s="4"/>
-    </row>
-    <row r="119" ht="12.0" customHeight="1">
+    </row>
+    <row r="119">
       <c r="A119" s="4"/>
       <c r="B119" s="4" t="s">
         <v>51</v>
@@ -4945,9 +6003,8 @@
       <c r="W119" s="4"/>
       <c r="X119" s="4"/>
       <c r="Y119" s="4"/>
-      <c r="Z119" s="4"/>
-    </row>
-    <row r="120" ht="12.0" customHeight="1">
+    </row>
+    <row r="120">
       <c r="A120" s="4"/>
       <c r="B120" s="4" t="s">
         <v>53</v>
@@ -4977,9 +6034,8 @@
       <c r="W120" s="4"/>
       <c r="X120" s="4"/>
       <c r="Y120" s="4"/>
-      <c r="Z120" s="4"/>
-    </row>
-    <row r="121" ht="12.0" customHeight="1">
+    </row>
+    <row r="121">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -5005,9 +6061,8 @@
       <c r="W121" s="4"/>
       <c r="X121" s="4"/>
       <c r="Y121" s="4"/>
-      <c r="Z121" s="4"/>
-    </row>
-    <row r="122" ht="12.0" customHeight="1">
+    </row>
+    <row r="122">
       <c r="A122" s="4" t="s">
         <v>83</v>
       </c>
@@ -5035,14 +6090,13 @@
       <c r="W122" s="4"/>
       <c r="X122" s="4"/>
       <c r="Y122" s="4"/>
-      <c r="Z122" s="4"/>
-    </row>
-    <row r="123" ht="12.0" customHeight="1">
+    </row>
+    <row r="123">
       <c r="A123" s="4"/>
       <c r="B123" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C123" s="28" t="s">
+      <c r="C123" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D123" s="4"/>
@@ -5067,9 +6121,8 @@
       <c r="W123" s="4"/>
       <c r="X123" s="4"/>
       <c r="Y123" s="4"/>
-      <c r="Z123" s="4"/>
-    </row>
-    <row r="124" ht="12.0" customHeight="1">
+    </row>
+    <row r="124">
       <c r="A124" s="4"/>
       <c r="B124" s="4" t="s">
         <v>40</v>
@@ -5099,14 +6152,13 @@
       <c r="W124" s="4"/>
       <c r="X124" s="4"/>
       <c r="Y124" s="4"/>
-      <c r="Z124" s="4"/>
-    </row>
-    <row r="125" ht="12.0" customHeight="1">
+    </row>
+    <row r="125">
       <c r="A125" s="4"/>
       <c r="B125" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C125" s="28" t="s">
+      <c r="C125" s="19" t="s">
         <v>79</v>
       </c>
       <c r="D125" s="4"/>
@@ -5131,9 +6183,8 @@
       <c r="W125" s="4"/>
       <c r="X125" s="4"/>
       <c r="Y125" s="4"/>
-      <c r="Z125" s="4"/>
-    </row>
-    <row r="126" ht="12.0" customHeight="1">
+    </row>
+    <row r="126">
       <c r="A126" s="4"/>
       <c r="B126" s="4" t="s">
         <v>43</v>
@@ -5163,9 +6214,8 @@
       <c r="W126" s="4"/>
       <c r="X126" s="4"/>
       <c r="Y126" s="4"/>
-      <c r="Z126" s="4"/>
-    </row>
-    <row r="127" ht="12.0" customHeight="1">
+    </row>
+    <row r="127">
       <c r="A127" s="4"/>
       <c r="B127" s="4" t="s">
         <v>44</v>
@@ -5195,14 +6245,13 @@
       <c r="W127" s="4"/>
       <c r="X127" s="4"/>
       <c r="Y127" s="4"/>
-      <c r="Z127" s="4"/>
-    </row>
-    <row r="128" ht="12.0" customHeight="1">
+    </row>
+    <row r="128">
       <c r="A128" s="4"/>
       <c r="B128" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C128" s="23">
+      <c r="C128" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D128" s="4"/>
@@ -5227,14 +6276,13 @@
       <c r="W128" s="4"/>
       <c r="X128" s="4"/>
       <c r="Y128" s="4"/>
-      <c r="Z128" s="4"/>
-    </row>
-    <row r="129" ht="12.0" customHeight="1">
+    </row>
+    <row r="129">
       <c r="A129" s="4"/>
       <c r="B129" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C129" s="24" t="s">
+      <c r="C129" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D129" s="4"/>
@@ -5259,14 +6307,13 @@
       <c r="W129" s="4"/>
       <c r="X129" s="4"/>
       <c r="Y129" s="4"/>
-      <c r="Z129" s="4"/>
-    </row>
-    <row r="130" ht="12.0" customHeight="1">
+    </row>
+    <row r="130">
       <c r="A130" s="4"/>
       <c r="B130" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C130" s="24" t="s">
+      <c r="C130" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D130" s="4"/>
@@ -5291,9 +6338,8 @@
       <c r="W130" s="4"/>
       <c r="X130" s="4"/>
       <c r="Y130" s="4"/>
-      <c r="Z130" s="4"/>
-    </row>
-    <row r="131" ht="12.0" customHeight="1">
+    </row>
+    <row r="131">
       <c r="A131" s="4"/>
       <c r="B131" s="4" t="s">
         <v>51</v>
@@ -5323,9 +6369,8 @@
       <c r="W131" s="4"/>
       <c r="X131" s="4"/>
       <c r="Y131" s="4"/>
-      <c r="Z131" s="4"/>
-    </row>
-    <row r="132" ht="12.0" customHeight="1">
+    </row>
+    <row r="132">
       <c r="A132" s="4"/>
       <c r="B132" s="4" t="s">
         <v>53</v>
@@ -5355,9 +6400,8 @@
       <c r="W132" s="4"/>
       <c r="X132" s="4"/>
       <c r="Y132" s="4"/>
-      <c r="Z132" s="4"/>
-    </row>
-    <row r="133" ht="12.0" customHeight="1">
+    </row>
+    <row r="133">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -5383,9 +6427,8 @@
       <c r="W133" s="4"/>
       <c r="X133" s="4"/>
       <c r="Y133" s="4"/>
-      <c r="Z133" s="4"/>
-    </row>
-    <row r="134" ht="12.0" customHeight="1">
+    </row>
+    <row r="134">
       <c r="A134" s="4" t="s">
         <v>85</v>
       </c>
@@ -5413,14 +6456,13 @@
       <c r="W134" s="4"/>
       <c r="X134" s="4"/>
       <c r="Y134" s="4"/>
-      <c r="Z134" s="4"/>
-    </row>
-    <row r="135" ht="12.0" customHeight="1">
+    </row>
+    <row r="135">
       <c r="A135" s="4"/>
       <c r="B135" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C135" s="28" t="s">
+      <c r="C135" s="19" t="s">
         <v>39</v>
       </c>
       <c r="D135" s="4"/>
@@ -5445,9 +6487,8 @@
       <c r="W135" s="4"/>
       <c r="X135" s="4"/>
       <c r="Y135" s="4"/>
-      <c r="Z135" s="4"/>
-    </row>
-    <row r="136" ht="12.0" customHeight="1">
+    </row>
+    <row r="136">
       <c r="A136" s="4"/>
       <c r="B136" s="4" t="s">
         <v>40</v>
@@ -5477,14 +6518,13 @@
       <c r="W136" s="4"/>
       <c r="X136" s="4"/>
       <c r="Y136" s="4"/>
-      <c r="Z136" s="4"/>
-    </row>
-    <row r="137" ht="12.0" customHeight="1">
+    </row>
+    <row r="137">
       <c r="A137" s="4"/>
       <c r="B137" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C137" s="28" t="s">
+      <c r="C137" s="19" t="s">
         <v>86</v>
       </c>
       <c r="D137" s="4"/>
@@ -5509,9 +6549,8 @@
       <c r="W137" s="4"/>
       <c r="X137" s="4"/>
       <c r="Y137" s="4"/>
-      <c r="Z137" s="4"/>
-    </row>
-    <row r="138" ht="12.0" customHeight="1">
+    </row>
+    <row r="138">
       <c r="A138" s="4"/>
       <c r="B138" s="4" t="s">
         <v>43</v>
@@ -5539,9 +6578,8 @@
       <c r="W138" s="4"/>
       <c r="X138" s="4"/>
       <c r="Y138" s="4"/>
-      <c r="Z138" s="4"/>
-    </row>
-    <row r="139" ht="12.0" customHeight="1">
+    </row>
+    <row r="139">
       <c r="A139" s="4"/>
       <c r="B139" s="4" t="s">
         <v>44</v>
@@ -5571,14 +6609,13 @@
       <c r="W139" s="4"/>
       <c r="X139" s="4"/>
       <c r="Y139" s="4"/>
-      <c r="Z139" s="4"/>
-    </row>
-    <row r="140" ht="12.0" customHeight="1">
+    </row>
+    <row r="140">
       <c r="A140" s="4"/>
       <c r="B140" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C140" s="23">
+      <c r="C140" s="20">
         <v>-1.0E20</v>
       </c>
       <c r="D140" s="4"/>
@@ -5603,14 +6640,13 @@
       <c r="W140" s="4"/>
       <c r="X140" s="4"/>
       <c r="Y140" s="4"/>
-      <c r="Z140" s="4"/>
-    </row>
-    <row r="141" ht="12.0" customHeight="1">
+    </row>
+    <row r="141">
       <c r="A141" s="4"/>
       <c r="B141" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C141" s="24" t="s">
+      <c r="C141" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D141" s="4"/>
@@ -5635,14 +6671,13 @@
       <c r="W141" s="4"/>
       <c r="X141" s="4"/>
       <c r="Y141" s="4"/>
-      <c r="Z141" s="4"/>
-    </row>
-    <row r="142" ht="12.0" customHeight="1">
+    </row>
+    <row r="142">
       <c r="A142" s="4"/>
       <c r="B142" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C142" s="24" t="s">
+      <c r="C142" s="21" t="s">
         <v>63</v>
       </c>
       <c r="D142" s="4"/>
@@ -5667,9 +6702,8 @@
       <c r="W142" s="4"/>
       <c r="X142" s="4"/>
       <c r="Y142" s="4"/>
-      <c r="Z142" s="4"/>
-    </row>
-    <row r="143" ht="12.0" customHeight="1">
+    </row>
+    <row r="143">
       <c r="A143" s="4"/>
       <c r="B143" s="4" t="s">
         <v>51</v>
@@ -5699,9 +6733,8 @@
       <c r="W143" s="4"/>
       <c r="X143" s="4"/>
       <c r="Y143" s="4"/>
-      <c r="Z143" s="4"/>
-    </row>
-    <row r="144" ht="12.0" customHeight="1">
+    </row>
+    <row r="144">
       <c r="A144" s="4"/>
       <c r="B144" s="4" t="s">
         <v>53</v>
@@ -5731,83 +6764,81 @@
       <c r="W144" s="4"/>
       <c r="X144" s="4"/>
       <c r="Y144" s="4"/>
-      <c r="Z144" s="4"/>
-    </row>
-    <row r="145" ht="12.0" customHeight="1"/>
-    <row r="146" ht="12.0" customHeight="1">
+    </row>
+    <row r="146">
       <c r="A146" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B146" s="4"/>
       <c r="C146" s="3"/>
     </row>
-    <row r="147" ht="12.0" customHeight="1">
+    <row r="147">
       <c r="A147" s="4"/>
       <c r="B147" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C147" s="28" t="s">
+      <c r="C147" s="19" t="s">
         <v>56</v>
       </c>
       <c r="D147" s="4"/>
     </row>
-    <row r="148" ht="12.0" customHeight="1">
+    <row r="148">
       <c r="A148" s="4"/>
       <c r="B148" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C148" s="7" t="s">
-        <v>89</v>
+      <c r="C148" s="24" t="s">
+        <v>41</v>
       </c>
       <c r="D148" s="4"/>
     </row>
-    <row r="149" ht="12.0" customHeight="1">
+    <row r="149">
       <c r="A149" s="4"/>
       <c r="B149" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C149" s="28">
+      <c r="C149" s="19">
         <v>1.0</v>
       </c>
       <c r="D149" s="4"/>
     </row>
-    <row r="150" ht="12.0" customHeight="1">
+    <row r="150">
       <c r="A150" s="4"/>
       <c r="B150" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C150" s="28"/>
+      <c r="C150" s="19"/>
       <c r="D150" s="4"/>
     </row>
-    <row r="151" ht="12.0" customHeight="1">
+    <row r="151">
       <c r="A151" s="4"/>
       <c r="B151" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C151" s="29" t="s">
-        <v>90</v>
+      <c r="C151" s="19" t="s">
+        <v>89</v>
       </c>
       <c r="D151" s="4"/>
     </row>
-    <row r="152" ht="12.0" customHeight="1">
+    <row r="152">
       <c r="A152" s="4"/>
       <c r="B152" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C152" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="C152" s="28" t="s">
-        <v>92</v>
-      </c>
       <c r="D152" s="4"/>
     </row>
-    <row r="153" ht="12.0" customHeight="1">
+    <row r="153">
       <c r="A153" s="4"/>
       <c r="B153" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C153" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C153" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D153" s="31"/>
+      <c r="D153" s="4"/>
     </row>
     <row r="154" ht="12.0" customHeight="1"/>
     <row r="155" ht="12.0" customHeight="1"/>
@@ -6009,658 +7040,653 @@
     <row r="351" ht="12.0" customHeight="1"/>
     <row r="352" ht="12.0" customHeight="1"/>
     <row r="353" ht="12.0" customHeight="1"/>
-    <row r="354" ht="12.0" customHeight="1"/>
-    <row r="355" ht="12.0" customHeight="1"/>
-    <row r="356" ht="12.0" customHeight="1"/>
-    <row r="357" ht="12.0" customHeight="1"/>
-    <row r="358" ht="12.0" customHeight="1"/>
-    <row r="359" ht="12.0" customHeight="1"/>
-    <row r="360" ht="12.0" customHeight="1"/>
-    <row r="361" ht="12.0" customHeight="1"/>
-    <row r="362" ht="12.0" customHeight="1"/>
-    <row r="363" ht="12.0" customHeight="1"/>
-    <row r="364" ht="12.0" customHeight="1"/>
-    <row r="365" ht="12.0" customHeight="1"/>
-    <row r="366" ht="12.0" customHeight="1"/>
-    <row r="367" ht="12.0" customHeight="1"/>
-    <row r="368" ht="12.0" customHeight="1"/>
-    <row r="369" ht="12.0" customHeight="1"/>
-    <row r="370" ht="12.0" customHeight="1"/>
-    <row r="371" ht="12.0" customHeight="1"/>
-    <row r="372" ht="12.0" customHeight="1"/>
-    <row r="373" ht="12.0" customHeight="1"/>
-    <row r="374" ht="12.0" customHeight="1"/>
-    <row r="375" ht="12.0" customHeight="1"/>
-    <row r="376" ht="12.0" customHeight="1"/>
-    <row r="377" ht="12.0" customHeight="1"/>
-    <row r="378" ht="12.0" customHeight="1"/>
-    <row r="379" ht="12.0" customHeight="1"/>
-    <row r="380" ht="12.0" customHeight="1"/>
-    <row r="381" ht="12.0" customHeight="1"/>
-    <row r="382" ht="12.0" customHeight="1"/>
-    <row r="383" ht="12.0" customHeight="1"/>
-    <row r="384" ht="12.0" customHeight="1"/>
-    <row r="385" ht="12.0" customHeight="1"/>
-    <row r="386" ht="12.0" customHeight="1"/>
-    <row r="387" ht="12.0" customHeight="1"/>
-    <row r="388" ht="12.0" customHeight="1"/>
-    <row r="389" ht="12.0" customHeight="1"/>
-    <row r="390" ht="12.0" customHeight="1"/>
-    <row r="391" ht="12.0" customHeight="1"/>
-    <row r="392" ht="12.0" customHeight="1"/>
-    <row r="393" ht="12.0" customHeight="1"/>
-    <row r="394" ht="12.0" customHeight="1"/>
-    <row r="395" ht="12.0" customHeight="1"/>
-    <row r="396" ht="12.0" customHeight="1"/>
-    <row r="397" ht="12.0" customHeight="1"/>
-    <row r="398" ht="12.0" customHeight="1"/>
-    <row r="399" ht="12.0" customHeight="1"/>
-    <row r="400" ht="12.0" customHeight="1"/>
-    <row r="401" ht="12.0" customHeight="1"/>
-    <row r="402" ht="12.0" customHeight="1"/>
-    <row r="403" ht="12.0" customHeight="1"/>
-    <row r="404" ht="12.0" customHeight="1"/>
-    <row r="405" ht="12.0" customHeight="1"/>
-    <row r="406" ht="12.0" customHeight="1"/>
-    <row r="407" ht="12.0" customHeight="1"/>
-    <row r="408" ht="12.0" customHeight="1"/>
-    <row r="409" ht="12.0" customHeight="1"/>
-    <row r="410" ht="12.0" customHeight="1"/>
-    <row r="411" ht="12.0" customHeight="1"/>
-    <row r="412" ht="12.0" customHeight="1"/>
-    <row r="413" ht="12.0" customHeight="1"/>
-    <row r="414" ht="12.0" customHeight="1"/>
-    <row r="415" ht="12.0" customHeight="1"/>
-    <row r="416" ht="12.0" customHeight="1"/>
-    <row r="417" ht="12.0" customHeight="1"/>
-    <row r="418" ht="12.0" customHeight="1"/>
-    <row r="419" ht="12.0" customHeight="1"/>
-    <row r="420" ht="12.0" customHeight="1"/>
-    <row r="421" ht="12.0" customHeight="1"/>
-    <row r="422" ht="12.0" customHeight="1"/>
-    <row r="423" ht="12.0" customHeight="1"/>
-    <row r="424" ht="12.0" customHeight="1"/>
-    <row r="425" ht="12.0" customHeight="1"/>
-    <row r="426" ht="12.0" customHeight="1"/>
-    <row r="427" ht="12.0" customHeight="1"/>
-    <row r="428" ht="12.0" customHeight="1"/>
-    <row r="429" ht="12.0" customHeight="1"/>
-    <row r="430" ht="12.0" customHeight="1"/>
-    <row r="431" ht="12.0" customHeight="1"/>
-    <row r="432" ht="12.0" customHeight="1"/>
-    <row r="433" ht="12.0" customHeight="1"/>
-    <row r="434" ht="12.0" customHeight="1"/>
-    <row r="435" ht="12.0" customHeight="1"/>
-    <row r="436" ht="12.0" customHeight="1"/>
-    <row r="437" ht="12.0" customHeight="1"/>
-    <row r="438" ht="12.0" customHeight="1"/>
-    <row r="439" ht="12.0" customHeight="1"/>
-    <row r="440" ht="12.0" customHeight="1"/>
-    <row r="441" ht="12.0" customHeight="1"/>
-    <row r="442" ht="12.0" customHeight="1"/>
-    <row r="443" ht="12.0" customHeight="1"/>
-    <row r="444" ht="12.0" customHeight="1"/>
-    <row r="445" ht="12.0" customHeight="1"/>
-    <row r="446" ht="12.0" customHeight="1"/>
-    <row r="447" ht="12.0" customHeight="1"/>
-    <row r="448" ht="12.0" customHeight="1"/>
-    <row r="449" ht="12.0" customHeight="1"/>
-    <row r="450" ht="12.0" customHeight="1"/>
-    <row r="451" ht="12.0" customHeight="1"/>
-    <row r="452" ht="12.0" customHeight="1"/>
-    <row r="453" ht="12.0" customHeight="1"/>
-    <row r="454" ht="12.0" customHeight="1"/>
-    <row r="455" ht="12.0" customHeight="1"/>
-    <row r="456" ht="12.0" customHeight="1"/>
-    <row r="457" ht="12.0" customHeight="1"/>
-    <row r="458" ht="12.0" customHeight="1"/>
-    <row r="459" ht="12.0" customHeight="1"/>
-    <row r="460" ht="12.0" customHeight="1"/>
-    <row r="461" ht="12.0" customHeight="1"/>
-    <row r="462" ht="12.0" customHeight="1"/>
-    <row r="463" ht="12.0" customHeight="1"/>
-    <row r="464" ht="12.0" customHeight="1"/>
-    <row r="465" ht="12.0" customHeight="1"/>
-    <row r="466" ht="12.0" customHeight="1"/>
-    <row r="467" ht="12.0" customHeight="1"/>
-    <row r="468" ht="12.0" customHeight="1"/>
-    <row r="469" ht="12.0" customHeight="1"/>
-    <row r="470" ht="12.0" customHeight="1"/>
-    <row r="471" ht="12.0" customHeight="1"/>
-    <row r="472" ht="12.0" customHeight="1"/>
-    <row r="473" ht="12.0" customHeight="1"/>
-    <row r="474" ht="12.0" customHeight="1"/>
-    <row r="475" ht="12.0" customHeight="1"/>
-    <row r="476" ht="12.0" customHeight="1"/>
-    <row r="477" ht="12.0" customHeight="1"/>
-    <row r="478" ht="12.0" customHeight="1"/>
-    <row r="479" ht="12.0" customHeight="1"/>
-    <row r="480" ht="12.0" customHeight="1"/>
-    <row r="481" ht="12.0" customHeight="1"/>
-    <row r="482" ht="12.0" customHeight="1"/>
-    <row r="483" ht="12.0" customHeight="1"/>
-    <row r="484" ht="12.0" customHeight="1"/>
-    <row r="485" ht="12.0" customHeight="1"/>
-    <row r="486" ht="12.0" customHeight="1"/>
-    <row r="487" ht="12.0" customHeight="1"/>
-    <row r="488" ht="12.0" customHeight="1"/>
-    <row r="489" ht="12.0" customHeight="1"/>
-    <row r="490" ht="12.0" customHeight="1"/>
-    <row r="491" ht="12.0" customHeight="1"/>
-    <row r="492" ht="12.0" customHeight="1"/>
-    <row r="493" ht="12.0" customHeight="1"/>
-    <row r="494" ht="12.0" customHeight="1"/>
-    <row r="495" ht="12.0" customHeight="1"/>
-    <row r="496" ht="12.0" customHeight="1"/>
-    <row r="497" ht="12.0" customHeight="1"/>
-    <row r="498" ht="12.0" customHeight="1"/>
-    <row r="499" ht="12.0" customHeight="1"/>
-    <row r="500" ht="12.0" customHeight="1"/>
-    <row r="501" ht="12.0" customHeight="1"/>
-    <row r="502" ht="12.0" customHeight="1"/>
-    <row r="503" ht="12.0" customHeight="1"/>
-    <row r="504" ht="12.0" customHeight="1"/>
-    <row r="505" ht="12.0" customHeight="1"/>
-    <row r="506" ht="12.0" customHeight="1"/>
-    <row r="507" ht="12.0" customHeight="1"/>
-    <row r="508" ht="12.0" customHeight="1"/>
-    <row r="509" ht="12.0" customHeight="1"/>
-    <row r="510" ht="12.0" customHeight="1"/>
-    <row r="511" ht="12.0" customHeight="1"/>
-    <row r="512" ht="12.0" customHeight="1"/>
-    <row r="513" ht="12.0" customHeight="1"/>
-    <row r="514" ht="12.0" customHeight="1"/>
-    <row r="515" ht="12.0" customHeight="1"/>
-    <row r="516" ht="12.0" customHeight="1"/>
-    <row r="517" ht="12.0" customHeight="1"/>
-    <row r="518" ht="12.0" customHeight="1"/>
-    <row r="519" ht="12.0" customHeight="1"/>
-    <row r="520" ht="12.0" customHeight="1"/>
-    <row r="521" ht="12.0" customHeight="1"/>
-    <row r="522" ht="12.0" customHeight="1"/>
-    <row r="523" ht="12.0" customHeight="1"/>
-    <row r="524" ht="12.0" customHeight="1"/>
-    <row r="525" ht="12.0" customHeight="1"/>
-    <row r="526" ht="12.0" customHeight="1"/>
-    <row r="527" ht="12.0" customHeight="1"/>
-    <row r="528" ht="12.0" customHeight="1"/>
-    <row r="529" ht="12.0" customHeight="1"/>
-    <row r="530" ht="12.0" customHeight="1"/>
-    <row r="531" ht="12.0" customHeight="1"/>
-    <row r="532" ht="12.0" customHeight="1"/>
-    <row r="533" ht="12.0" customHeight="1"/>
-    <row r="534" ht="12.0" customHeight="1"/>
-    <row r="535" ht="12.0" customHeight="1"/>
-    <row r="536" ht="12.0" customHeight="1"/>
-    <row r="537" ht="12.0" customHeight="1"/>
-    <row r="538" ht="12.0" customHeight="1"/>
-    <row r="539" ht="12.0" customHeight="1"/>
-    <row r="540" ht="12.0" customHeight="1"/>
-    <row r="541" ht="12.0" customHeight="1"/>
-    <row r="542" ht="12.0" customHeight="1"/>
-    <row r="543" ht="12.0" customHeight="1"/>
-    <row r="544" ht="12.0" customHeight="1"/>
-    <row r="545" ht="12.0" customHeight="1"/>
-    <row r="546" ht="12.0" customHeight="1"/>
-    <row r="547" ht="12.0" customHeight="1"/>
-    <row r="548" ht="12.0" customHeight="1"/>
-    <row r="549" ht="12.0" customHeight="1"/>
-    <row r="550" ht="12.0" customHeight="1"/>
-    <row r="551" ht="12.0" customHeight="1"/>
-    <row r="552" ht="12.0" customHeight="1"/>
-    <row r="553" ht="12.0" customHeight="1"/>
-    <row r="554" ht="12.0" customHeight="1"/>
-    <row r="555" ht="12.0" customHeight="1"/>
-    <row r="556" ht="12.0" customHeight="1"/>
-    <row r="557" ht="12.0" customHeight="1"/>
-    <row r="558" ht="12.0" customHeight="1"/>
-    <row r="559" ht="12.0" customHeight="1"/>
-    <row r="560" ht="12.0" customHeight="1"/>
-    <row r="561" ht="12.0" customHeight="1"/>
-    <row r="562" ht="12.0" customHeight="1"/>
-    <row r="563" ht="12.0" customHeight="1"/>
-    <row r="564" ht="12.0" customHeight="1"/>
-    <row r="565" ht="12.0" customHeight="1"/>
-    <row r="566" ht="12.0" customHeight="1"/>
-    <row r="567" ht="12.0" customHeight="1"/>
-    <row r="568" ht="12.0" customHeight="1"/>
-    <row r="569" ht="12.0" customHeight="1"/>
-    <row r="570" ht="12.0" customHeight="1"/>
-    <row r="571" ht="12.0" customHeight="1"/>
-    <row r="572" ht="12.0" customHeight="1"/>
-    <row r="573" ht="12.0" customHeight="1"/>
-    <row r="574" ht="12.0" customHeight="1"/>
-    <row r="575" ht="12.0" customHeight="1"/>
-    <row r="576" ht="12.0" customHeight="1"/>
-    <row r="577" ht="12.0" customHeight="1"/>
-    <row r="578" ht="12.0" customHeight="1"/>
-    <row r="579" ht="12.0" customHeight="1"/>
-    <row r="580" ht="12.0" customHeight="1"/>
-    <row r="581" ht="12.0" customHeight="1"/>
-    <row r="582" ht="12.0" customHeight="1"/>
-    <row r="583" ht="12.0" customHeight="1"/>
-    <row r="584" ht="12.0" customHeight="1"/>
-    <row r="585" ht="12.0" customHeight="1"/>
-    <row r="586" ht="12.0" customHeight="1"/>
-    <row r="587" ht="12.0" customHeight="1"/>
-    <row r="588" ht="12.0" customHeight="1"/>
-    <row r="589" ht="12.0" customHeight="1"/>
-    <row r="590" ht="12.0" customHeight="1"/>
-    <row r="591" ht="12.0" customHeight="1"/>
-    <row r="592" ht="12.0" customHeight="1"/>
-    <row r="593" ht="12.0" customHeight="1"/>
-    <row r="594" ht="12.0" customHeight="1"/>
-    <row r="595" ht="12.0" customHeight="1"/>
-    <row r="596" ht="12.0" customHeight="1"/>
-    <row r="597" ht="12.0" customHeight="1"/>
-    <row r="598" ht="12.0" customHeight="1"/>
-    <row r="599" ht="12.0" customHeight="1"/>
-    <row r="600" ht="12.0" customHeight="1"/>
-    <row r="601" ht="12.0" customHeight="1"/>
-    <row r="602" ht="12.0" customHeight="1"/>
-    <row r="603" ht="12.0" customHeight="1"/>
-    <row r="604" ht="12.0" customHeight="1"/>
-    <row r="605" ht="12.0" customHeight="1"/>
-    <row r="606" ht="12.0" customHeight="1"/>
-    <row r="607" ht="12.0" customHeight="1"/>
-    <row r="608" ht="12.0" customHeight="1"/>
-    <row r="609" ht="12.0" customHeight="1"/>
-    <row r="610" ht="12.0" customHeight="1"/>
-    <row r="611" ht="12.0" customHeight="1"/>
-    <row r="612" ht="12.0" customHeight="1"/>
-    <row r="613" ht="12.0" customHeight="1"/>
-    <row r="614" ht="12.0" customHeight="1"/>
-    <row r="615" ht="12.0" customHeight="1"/>
-    <row r="616" ht="12.0" customHeight="1"/>
-    <row r="617" ht="12.0" customHeight="1"/>
-    <row r="618" ht="12.0" customHeight="1"/>
-    <row r="619" ht="12.0" customHeight="1"/>
-    <row r="620" ht="12.0" customHeight="1"/>
-    <row r="621" ht="12.0" customHeight="1"/>
-    <row r="622" ht="12.0" customHeight="1"/>
-    <row r="623" ht="12.0" customHeight="1"/>
-    <row r="624" ht="12.0" customHeight="1"/>
-    <row r="625" ht="12.0" customHeight="1"/>
-    <row r="626" ht="12.0" customHeight="1"/>
-    <row r="627" ht="12.0" customHeight="1"/>
-    <row r="628" ht="12.0" customHeight="1"/>
-    <row r="629" ht="12.0" customHeight="1"/>
-    <row r="630" ht="12.0" customHeight="1"/>
-    <row r="631" ht="12.0" customHeight="1"/>
-    <row r="632" ht="12.0" customHeight="1"/>
-    <row r="633" ht="12.0" customHeight="1"/>
-    <row r="634" ht="12.0" customHeight="1"/>
-    <row r="635" ht="12.0" customHeight="1"/>
-    <row r="636" ht="12.0" customHeight="1"/>
-    <row r="637" ht="12.0" customHeight="1"/>
-    <row r="638" ht="12.0" customHeight="1"/>
-    <row r="639" ht="12.0" customHeight="1"/>
-    <row r="640" ht="12.0" customHeight="1"/>
-    <row r="641" ht="12.0" customHeight="1"/>
-    <row r="642" ht="12.0" customHeight="1"/>
-    <row r="643" ht="12.0" customHeight="1"/>
-    <row r="644" ht="12.0" customHeight="1"/>
-    <row r="645" ht="12.0" customHeight="1"/>
-    <row r="646" ht="12.0" customHeight="1"/>
-    <row r="647" ht="12.0" customHeight="1"/>
-    <row r="648" ht="12.0" customHeight="1"/>
-    <row r="649" ht="12.0" customHeight="1"/>
-    <row r="650" ht="12.0" customHeight="1"/>
-    <row r="651" ht="12.0" customHeight="1"/>
-    <row r="652" ht="12.0" customHeight="1"/>
-    <row r="653" ht="12.0" customHeight="1"/>
-    <row r="654" ht="12.0" customHeight="1"/>
-    <row r="655" ht="12.0" customHeight="1"/>
-    <row r="656" ht="12.0" customHeight="1"/>
-    <row r="657" ht="12.0" customHeight="1"/>
-    <row r="658" ht="12.0" customHeight="1"/>
-    <row r="659" ht="12.0" customHeight="1"/>
-    <row r="660" ht="12.0" customHeight="1"/>
-    <row r="661" ht="12.0" customHeight="1"/>
-    <row r="662" ht="12.0" customHeight="1"/>
-    <row r="663" ht="12.0" customHeight="1"/>
-    <row r="664" ht="12.0" customHeight="1"/>
-    <row r="665" ht="12.0" customHeight="1"/>
-    <row r="666" ht="12.0" customHeight="1"/>
-    <row r="667" ht="12.0" customHeight="1"/>
-    <row r="668" ht="12.0" customHeight="1"/>
-    <row r="669" ht="12.0" customHeight="1"/>
-    <row r="670" ht="12.0" customHeight="1"/>
-    <row r="671" ht="12.0" customHeight="1"/>
-    <row r="672" ht="12.0" customHeight="1"/>
-    <row r="673" ht="12.0" customHeight="1"/>
-    <row r="674" ht="12.0" customHeight="1"/>
-    <row r="675" ht="12.0" customHeight="1"/>
-    <row r="676" ht="12.0" customHeight="1"/>
-    <row r="677" ht="12.0" customHeight="1"/>
-    <row r="678" ht="12.0" customHeight="1"/>
-    <row r="679" ht="12.0" customHeight="1"/>
-    <row r="680" ht="12.0" customHeight="1"/>
-    <row r="681" ht="12.0" customHeight="1"/>
-    <row r="682" ht="12.0" customHeight="1"/>
-    <row r="683" ht="12.0" customHeight="1"/>
-    <row r="684" ht="12.0" customHeight="1"/>
-    <row r="685" ht="12.0" customHeight="1"/>
-    <row r="686" ht="12.0" customHeight="1"/>
-    <row r="687" ht="12.0" customHeight="1"/>
-    <row r="688" ht="12.0" customHeight="1"/>
-    <row r="689" ht="12.0" customHeight="1"/>
-    <row r="690" ht="12.0" customHeight="1"/>
-    <row r="691" ht="12.0" customHeight="1"/>
-    <row r="692" ht="12.0" customHeight="1"/>
-    <row r="693" ht="12.0" customHeight="1"/>
-    <row r="694" ht="12.0" customHeight="1"/>
-    <row r="695" ht="12.0" customHeight="1"/>
-    <row r="696" ht="12.0" customHeight="1"/>
-    <row r="697" ht="12.0" customHeight="1"/>
-    <row r="698" ht="12.0" customHeight="1"/>
-    <row r="699" ht="12.0" customHeight="1"/>
-    <row r="700" ht="12.0" customHeight="1"/>
-    <row r="701" ht="12.0" customHeight="1"/>
-    <row r="702" ht="12.0" customHeight="1"/>
-    <row r="703" ht="12.0" customHeight="1"/>
-    <row r="704" ht="12.0" customHeight="1"/>
-    <row r="705" ht="12.0" customHeight="1"/>
-    <row r="706" ht="12.0" customHeight="1"/>
-    <row r="707" ht="12.0" customHeight="1"/>
-    <row r="708" ht="12.0" customHeight="1"/>
-    <row r="709" ht="12.0" customHeight="1"/>
-    <row r="710" ht="12.0" customHeight="1"/>
-    <row r="711" ht="12.0" customHeight="1"/>
-    <row r="712" ht="12.0" customHeight="1"/>
-    <row r="713" ht="12.0" customHeight="1"/>
-    <row r="714" ht="12.0" customHeight="1"/>
-    <row r="715" ht="12.0" customHeight="1"/>
-    <row r="716" ht="12.0" customHeight="1"/>
-    <row r="717" ht="12.0" customHeight="1"/>
-    <row r="718" ht="12.0" customHeight="1"/>
-    <row r="719" ht="12.0" customHeight="1"/>
-    <row r="720" ht="12.0" customHeight="1"/>
-    <row r="721" ht="12.0" customHeight="1"/>
-    <row r="722" ht="12.0" customHeight="1"/>
-    <row r="723" ht="12.0" customHeight="1"/>
-    <row r="724" ht="12.0" customHeight="1"/>
-    <row r="725" ht="12.0" customHeight="1"/>
-    <row r="726" ht="12.0" customHeight="1"/>
-    <row r="727" ht="12.0" customHeight="1"/>
-    <row r="728" ht="12.0" customHeight="1"/>
-    <row r="729" ht="12.0" customHeight="1"/>
-    <row r="730" ht="12.0" customHeight="1"/>
-    <row r="731" ht="12.0" customHeight="1"/>
-    <row r="732" ht="12.0" customHeight="1"/>
-    <row r="733" ht="12.0" customHeight="1"/>
-    <row r="734" ht="12.0" customHeight="1"/>
-    <row r="735" ht="12.0" customHeight="1"/>
-    <row r="736" ht="12.0" customHeight="1"/>
-    <row r="737" ht="12.0" customHeight="1"/>
-    <row r="738" ht="12.0" customHeight="1"/>
-    <row r="739" ht="12.0" customHeight="1"/>
-    <row r="740" ht="12.0" customHeight="1"/>
-    <row r="741" ht="12.0" customHeight="1"/>
-    <row r="742" ht="12.0" customHeight="1"/>
-    <row r="743" ht="12.0" customHeight="1"/>
-    <row r="744" ht="12.0" customHeight="1"/>
-    <row r="745" ht="12.0" customHeight="1"/>
-    <row r="746" ht="12.0" customHeight="1"/>
-    <row r="747" ht="12.0" customHeight="1"/>
-    <row r="748" ht="12.0" customHeight="1"/>
-    <row r="749" ht="12.0" customHeight="1"/>
-    <row r="750" ht="12.0" customHeight="1"/>
-    <row r="751" ht="12.0" customHeight="1"/>
-    <row r="752" ht="12.0" customHeight="1"/>
-    <row r="753" ht="12.0" customHeight="1"/>
-    <row r="754" ht="12.0" customHeight="1"/>
-    <row r="755" ht="12.0" customHeight="1"/>
-    <row r="756" ht="12.0" customHeight="1"/>
-    <row r="757" ht="12.0" customHeight="1"/>
-    <row r="758" ht="12.0" customHeight="1"/>
-    <row r="759" ht="12.0" customHeight="1"/>
-    <row r="760" ht="12.0" customHeight="1"/>
-    <row r="761" ht="12.0" customHeight="1"/>
-    <row r="762" ht="12.0" customHeight="1"/>
-    <row r="763" ht="12.0" customHeight="1"/>
-    <row r="764" ht="12.0" customHeight="1"/>
-    <row r="765" ht="12.0" customHeight="1"/>
-    <row r="766" ht="12.0" customHeight="1"/>
-    <row r="767" ht="12.0" customHeight="1"/>
-    <row r="768" ht="12.0" customHeight="1"/>
-    <row r="769" ht="12.0" customHeight="1"/>
-    <row r="770" ht="12.0" customHeight="1"/>
-    <row r="771" ht="12.0" customHeight="1"/>
-    <row r="772" ht="12.0" customHeight="1"/>
-    <row r="773" ht="12.0" customHeight="1"/>
-    <row r="774" ht="12.0" customHeight="1"/>
-    <row r="775" ht="12.0" customHeight="1"/>
-    <row r="776" ht="12.0" customHeight="1"/>
-    <row r="777" ht="12.0" customHeight="1"/>
-    <row r="778" ht="12.0" customHeight="1"/>
-    <row r="779" ht="12.0" customHeight="1"/>
-    <row r="780" ht="12.0" customHeight="1"/>
-    <row r="781" ht="12.0" customHeight="1"/>
-    <row r="782" ht="12.0" customHeight="1"/>
-    <row r="783" ht="12.0" customHeight="1"/>
-    <row r="784" ht="12.0" customHeight="1"/>
-    <row r="785" ht="12.0" customHeight="1"/>
-    <row r="786" ht="12.0" customHeight="1"/>
-    <row r="787" ht="12.0" customHeight="1"/>
-    <row r="788" ht="12.0" customHeight="1"/>
-    <row r="789" ht="12.0" customHeight="1"/>
-    <row r="790" ht="12.0" customHeight="1"/>
-    <row r="791" ht="12.0" customHeight="1"/>
-    <row r="792" ht="12.0" customHeight="1"/>
-    <row r="793" ht="12.0" customHeight="1"/>
-    <row r="794" ht="12.0" customHeight="1"/>
-    <row r="795" ht="12.0" customHeight="1"/>
-    <row r="796" ht="12.0" customHeight="1"/>
-    <row r="797" ht="12.0" customHeight="1"/>
-    <row r="798" ht="12.0" customHeight="1"/>
-    <row r="799" ht="12.0" customHeight="1"/>
-    <row r="800" ht="12.0" customHeight="1"/>
-    <row r="801" ht="12.0" customHeight="1"/>
-    <row r="802" ht="12.0" customHeight="1"/>
-    <row r="803" ht="12.0" customHeight="1"/>
-    <row r="804" ht="12.0" customHeight="1"/>
-    <row r="805" ht="12.0" customHeight="1"/>
-    <row r="806" ht="12.0" customHeight="1"/>
-    <row r="807" ht="12.0" customHeight="1"/>
-    <row r="808" ht="12.0" customHeight="1"/>
-    <row r="809" ht="12.0" customHeight="1"/>
-    <row r="810" ht="12.0" customHeight="1"/>
-    <row r="811" ht="12.0" customHeight="1"/>
-    <row r="812" ht="12.0" customHeight="1"/>
-    <row r="813" ht="12.0" customHeight="1"/>
-    <row r="814" ht="12.0" customHeight="1"/>
-    <row r="815" ht="12.0" customHeight="1"/>
-    <row r="816" ht="12.0" customHeight="1"/>
-    <row r="817" ht="12.0" customHeight="1"/>
-    <row r="818" ht="12.0" customHeight="1"/>
-    <row r="819" ht="12.0" customHeight="1"/>
-    <row r="820" ht="12.0" customHeight="1"/>
-    <row r="821" ht="12.0" customHeight="1"/>
-    <row r="822" ht="12.0" customHeight="1"/>
-    <row r="823" ht="12.0" customHeight="1"/>
-    <row r="824" ht="12.0" customHeight="1"/>
-    <row r="825" ht="12.0" customHeight="1"/>
-    <row r="826" ht="12.0" customHeight="1"/>
-    <row r="827" ht="12.0" customHeight="1"/>
-    <row r="828" ht="12.0" customHeight="1"/>
-    <row r="829" ht="12.0" customHeight="1"/>
-    <row r="830" ht="12.0" customHeight="1"/>
-    <row r="831" ht="12.0" customHeight="1"/>
-    <row r="832" ht="12.0" customHeight="1"/>
-    <row r="833" ht="12.0" customHeight="1"/>
-    <row r="834" ht="12.0" customHeight="1"/>
-    <row r="835" ht="12.0" customHeight="1"/>
-    <row r="836" ht="12.0" customHeight="1"/>
-    <row r="837" ht="12.0" customHeight="1"/>
-    <row r="838" ht="12.0" customHeight="1"/>
-    <row r="839" ht="12.0" customHeight="1"/>
-    <row r="840" ht="12.0" customHeight="1"/>
-    <row r="841" ht="12.0" customHeight="1"/>
-    <row r="842" ht="12.0" customHeight="1"/>
-    <row r="843" ht="12.0" customHeight="1"/>
-    <row r="844" ht="12.0" customHeight="1"/>
-    <row r="845" ht="12.0" customHeight="1"/>
-    <row r="846" ht="12.0" customHeight="1"/>
-    <row r="847" ht="12.0" customHeight="1"/>
-    <row r="848" ht="12.0" customHeight="1"/>
-    <row r="849" ht="12.0" customHeight="1"/>
-    <row r="850" ht="12.0" customHeight="1"/>
-    <row r="851" ht="12.0" customHeight="1"/>
-    <row r="852" ht="12.0" customHeight="1"/>
-    <row r="853" ht="12.0" customHeight="1"/>
-    <row r="854" ht="12.0" customHeight="1"/>
-    <row r="855" ht="12.0" customHeight="1"/>
-    <row r="856" ht="12.0" customHeight="1"/>
-    <row r="857" ht="12.0" customHeight="1"/>
-    <row r="858" ht="12.0" customHeight="1"/>
-    <row r="859" ht="12.0" customHeight="1"/>
-    <row r="860" ht="12.0" customHeight="1"/>
-    <row r="861" ht="12.0" customHeight="1"/>
-    <row r="862" ht="12.0" customHeight="1"/>
-    <row r="863" ht="12.0" customHeight="1"/>
-    <row r="864" ht="12.0" customHeight="1"/>
-    <row r="865" ht="12.0" customHeight="1"/>
-    <row r="866" ht="12.0" customHeight="1"/>
-    <row r="867" ht="12.0" customHeight="1"/>
-    <row r="868" ht="12.0" customHeight="1"/>
-    <row r="869" ht="12.0" customHeight="1"/>
-    <row r="870" ht="12.0" customHeight="1"/>
-    <row r="871" ht="12.0" customHeight="1"/>
-    <row r="872" ht="12.0" customHeight="1"/>
-    <row r="873" ht="12.0" customHeight="1"/>
-    <row r="874" ht="12.0" customHeight="1"/>
-    <row r="875" ht="12.0" customHeight="1"/>
-    <row r="876" ht="12.0" customHeight="1"/>
-    <row r="877" ht="12.0" customHeight="1"/>
-    <row r="878" ht="12.0" customHeight="1"/>
-    <row r="879" ht="12.0" customHeight="1"/>
-    <row r="880" ht="12.0" customHeight="1"/>
-    <row r="881" ht="12.0" customHeight="1"/>
-    <row r="882" ht="12.0" customHeight="1"/>
-    <row r="883" ht="12.0" customHeight="1"/>
-    <row r="884" ht="12.0" customHeight="1"/>
-    <row r="885" ht="12.0" customHeight="1"/>
-    <row r="886" ht="12.0" customHeight="1"/>
-    <row r="887" ht="12.0" customHeight="1"/>
-    <row r="888" ht="12.0" customHeight="1"/>
-    <row r="889" ht="12.0" customHeight="1"/>
-    <row r="890" ht="12.0" customHeight="1"/>
-    <row r="891" ht="12.0" customHeight="1"/>
-    <row r="892" ht="12.0" customHeight="1"/>
-    <row r="893" ht="12.0" customHeight="1"/>
-    <row r="894" ht="12.0" customHeight="1"/>
-    <row r="895" ht="12.0" customHeight="1"/>
-    <row r="896" ht="12.0" customHeight="1"/>
-    <row r="897" ht="12.0" customHeight="1"/>
-    <row r="898" ht="12.0" customHeight="1"/>
-    <row r="899" ht="12.0" customHeight="1"/>
-    <row r="900" ht="12.0" customHeight="1"/>
-    <row r="901" ht="12.0" customHeight="1"/>
-    <row r="902" ht="12.0" customHeight="1"/>
-    <row r="903" ht="12.0" customHeight="1"/>
-    <row r="904" ht="12.0" customHeight="1"/>
-    <row r="905" ht="12.0" customHeight="1"/>
-    <row r="906" ht="12.0" customHeight="1"/>
-    <row r="907" ht="12.0" customHeight="1"/>
-    <row r="908" ht="12.0" customHeight="1"/>
-    <row r="909" ht="12.0" customHeight="1"/>
-    <row r="910" ht="12.0" customHeight="1"/>
-    <row r="911" ht="12.0" customHeight="1"/>
-    <row r="912" ht="12.0" customHeight="1"/>
-    <row r="913" ht="12.0" customHeight="1"/>
-    <row r="914" ht="12.0" customHeight="1"/>
-    <row r="915" ht="12.0" customHeight="1"/>
-    <row r="916" ht="12.0" customHeight="1"/>
-    <row r="917" ht="12.0" customHeight="1"/>
-    <row r="918" ht="12.0" customHeight="1"/>
-    <row r="919" ht="12.0" customHeight="1"/>
-    <row r="920" ht="12.0" customHeight="1"/>
-    <row r="921" ht="12.0" customHeight="1"/>
-    <row r="922" ht="12.0" customHeight="1"/>
-    <row r="923" ht="12.0" customHeight="1"/>
-    <row r="924" ht="12.0" customHeight="1"/>
-    <row r="925" ht="12.0" customHeight="1"/>
-    <row r="926" ht="12.0" customHeight="1"/>
-    <row r="927" ht="12.0" customHeight="1"/>
-    <row r="928" ht="12.0" customHeight="1"/>
-    <row r="929" ht="12.0" customHeight="1"/>
-    <row r="930" ht="12.0" customHeight="1"/>
-    <row r="931" ht="12.0" customHeight="1"/>
-    <row r="932" ht="12.0" customHeight="1"/>
-    <row r="933" ht="12.0" customHeight="1"/>
-    <row r="934" ht="12.0" customHeight="1"/>
-    <row r="935" ht="12.0" customHeight="1"/>
-    <row r="936" ht="12.0" customHeight="1"/>
-    <row r="937" ht="12.0" customHeight="1"/>
-    <row r="938" ht="12.0" customHeight="1"/>
-    <row r="939" ht="12.0" customHeight="1"/>
-    <row r="940" ht="12.0" customHeight="1"/>
-    <row r="941" ht="12.0" customHeight="1"/>
-    <row r="942" ht="12.0" customHeight="1"/>
-    <row r="943" ht="12.0" customHeight="1"/>
-    <row r="944" ht="12.0" customHeight="1"/>
-    <row r="945" ht="12.0" customHeight="1"/>
-    <row r="946" ht="12.0" customHeight="1"/>
-    <row r="947" ht="12.0" customHeight="1"/>
-    <row r="948" ht="12.0" customHeight="1"/>
-    <row r="949" ht="12.0" customHeight="1"/>
-    <row r="950" ht="12.0" customHeight="1"/>
-    <row r="951" ht="12.0" customHeight="1"/>
-    <row r="952" ht="12.0" customHeight="1"/>
-    <row r="953" ht="12.0" customHeight="1"/>
-    <row r="954" ht="12.0" customHeight="1"/>
-    <row r="955" ht="12.0" customHeight="1"/>
-    <row r="956" ht="12.0" customHeight="1"/>
-    <row r="957" ht="12.0" customHeight="1"/>
-    <row r="958" ht="12.0" customHeight="1"/>
-    <row r="959" ht="12.0" customHeight="1"/>
-    <row r="960" ht="12.0" customHeight="1"/>
-    <row r="961" ht="12.0" customHeight="1"/>
-    <row r="962" ht="12.0" customHeight="1"/>
-    <row r="963" ht="12.0" customHeight="1"/>
-    <row r="964" ht="12.0" customHeight="1"/>
-    <row r="965" ht="12.0" customHeight="1"/>
-    <row r="966" ht="12.0" customHeight="1"/>
-    <row r="967" ht="12.0" customHeight="1"/>
-    <row r="968" ht="12.0" customHeight="1"/>
-    <row r="969" ht="12.0" customHeight="1"/>
-    <row r="970" ht="12.0" customHeight="1"/>
-    <row r="971" ht="12.0" customHeight="1"/>
-    <row r="972" ht="12.0" customHeight="1"/>
-    <row r="973" ht="12.0" customHeight="1"/>
-    <row r="974" ht="12.0" customHeight="1"/>
-    <row r="975" ht="12.0" customHeight="1"/>
-    <row r="976" ht="12.0" customHeight="1"/>
-    <row r="977" ht="12.0" customHeight="1"/>
-    <row r="978" ht="12.0" customHeight="1"/>
-    <row r="979" ht="12.0" customHeight="1"/>
-    <row r="980" ht="12.0" customHeight="1"/>
-    <row r="981" ht="12.0" customHeight="1"/>
-    <row r="982" ht="12.0" customHeight="1"/>
-    <row r="983" ht="12.0" customHeight="1"/>
-    <row r="984" ht="12.0" customHeight="1"/>
-    <row r="985" ht="12.0" customHeight="1"/>
-    <row r="986" ht="12.0" customHeight="1"/>
-    <row r="987" ht="12.0" customHeight="1"/>
-    <row r="988" ht="12.0" customHeight="1"/>
-    <row r="989" ht="12.0" customHeight="1"/>
-    <row r="990" ht="12.0" customHeight="1"/>
-    <row r="991" ht="12.0" customHeight="1"/>
-    <row r="992" ht="12.0" customHeight="1"/>
-    <row r="993" ht="12.0" customHeight="1"/>
-    <row r="994" ht="12.0" customHeight="1"/>
-    <row r="995" ht="12.0" customHeight="1"/>
-    <row r="996" ht="12.0" customHeight="1"/>
-    <row r="997" ht="12.0" customHeight="1"/>
-    <row r="998" ht="12.0" customHeight="1"/>
-    <row r="999" ht="12.0" customHeight="1"/>
-    <row r="1000" ht="12.0" customHeight="1"/>
-    <row r="1001" ht="12.0" customHeight="1"/>
-    <row r="1002" ht="12.0" customHeight="1"/>
-    <row r="1003" ht="12.0" customHeight="1"/>
-    <row r="1004" ht="12.0" customHeight="1"/>
-    <row r="1005" ht="12.0" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/product-definitions/spreadsheet/cloud-coverage.xlsx
+++ b/product-definitions/spreadsheet/cloud-coverage.xlsx
@@ -307,7 +307,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -327,11 +327,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
@@ -379,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -395,57 +390,50 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
@@ -2958,36 +2946,36 @@
       <c r="F1" s="13"/>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="5" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -2995,18 +2983,18 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="15">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -3014,42 +3002,42 @@
       <c r="B9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>48</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="18"/>
+      <c r="F9" s="17"/>
     </row>
     <row r="10">
       <c r="B10" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="16" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="18"/>
+      <c r="F10" s="17"/>
     </row>
     <row r="11">
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="14" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="15"/>
+      <c r="C13" s="14"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
@@ -3057,31 +3045,31 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="14" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="14" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="5"/>
@@ -3090,57 +3078,57 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="14" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="16">
+      <c r="C20" s="15">
         <v>-127.0</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="17" t="s">
+      <c r="C21" s="16" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="14" t="s">
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="B23" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="14" t="s">
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="B24" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="25">
-      <c r="C25" s="15"/>
-    </row>
-    <row r="26">
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="C25" s="14"/>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>59</v>
       </c>
@@ -3169,12 +3157,12 @@
       <c r="X26" s="4"/>
       <c r="Y26" s="4"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D27" s="4"/>
@@ -3200,7 +3188,7 @@
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>40</v>
@@ -3231,7 +3219,7 @@
       <c r="X28" s="4"/>
       <c r="Y28" s="4"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
         <v>29</v>
@@ -3262,7 +3250,7 @@
       <c r="X29" s="4"/>
       <c r="Y29" s="4"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
         <v>43</v>
@@ -3293,7 +3281,7 @@
       <c r="X30" s="4"/>
       <c r="Y30" s="4"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
         <v>44</v>
@@ -3324,12 +3312,12 @@
       <c r="X31" s="4"/>
       <c r="Y31" s="4"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D32" s="4"/>
@@ -3355,12 +3343,12 @@
       <c r="X32" s="4"/>
       <c r="Y32" s="4"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="C33" s="19" t="s">
         <v>63</v>
       </c>
       <c r="D33" s="4"/>
@@ -3386,12 +3374,12 @@
       <c r="X33" s="4"/>
       <c r="Y33" s="4"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="4"/>
       <c r="B34" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="19" t="s">
         <v>63</v>
       </c>
       <c r="D34" s="4"/>
@@ -3417,7 +3405,7 @@
       <c r="X34" s="4"/>
       <c r="Y34" s="4"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="4"/>
       <c r="B35" s="4" t="s">
         <v>51</v>
@@ -3448,7 +3436,7 @@
       <c r="X35" s="4"/>
       <c r="Y35" s="4"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="4"/>
       <c r="B36" s="4" t="s">
         <v>53</v>
@@ -3479,7 +3467,7 @@
       <c r="X36" s="4"/>
       <c r="Y36" s="4"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -3506,7 +3494,7 @@
       <c r="X37" s="4"/>
       <c r="Y37" s="4"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>64</v>
       </c>
@@ -3535,12 +3523,12 @@
       <c r="X38" s="4"/>
       <c r="Y38" s="4"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="4"/>
       <c r="B39" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D39" s="4"/>
@@ -3566,7 +3554,7 @@
       <c r="X39" s="4"/>
       <c r="Y39" s="4"/>
     </row>
-    <row r="40">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="4"/>
       <c r="B40" s="4" t="s">
         <v>40</v>
@@ -3597,7 +3585,7 @@
       <c r="X40" s="4"/>
       <c r="Y40" s="4"/>
     </row>
-    <row r="41">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="4"/>
       <c r="B41" s="4" t="s">
         <v>29</v>
@@ -3628,7 +3616,7 @@
       <c r="X41" s="4"/>
       <c r="Y41" s="4"/>
     </row>
-    <row r="42">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="4"/>
       <c r="B42" s="4" t="s">
         <v>43</v>
@@ -3659,7 +3647,7 @@
       <c r="X42" s="4"/>
       <c r="Y42" s="4"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="4"/>
       <c r="B43" s="4" t="s">
         <v>44</v>
@@ -3690,12 +3678,12 @@
       <c r="X43" s="4"/>
       <c r="Y43" s="4"/>
     </row>
-    <row r="44">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="4"/>
       <c r="B44" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="20">
+      <c r="C44" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D44" s="4"/>
@@ -3721,12 +3709,12 @@
       <c r="X44" s="4"/>
       <c r="Y44" s="4"/>
     </row>
-    <row r="45">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="21" t="s">
+      <c r="C45" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D45" s="4"/>
@@ -3752,12 +3740,12 @@
       <c r="X45" s="4"/>
       <c r="Y45" s="4"/>
     </row>
-    <row r="46">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="4"/>
       <c r="B46" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="C46" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D46" s="4"/>
@@ -3783,7 +3771,7 @@
       <c r="X46" s="4"/>
       <c r="Y46" s="4"/>
     </row>
-    <row r="47">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="4"/>
       <c r="B47" s="4" t="s">
         <v>51</v>
@@ -3814,7 +3802,7 @@
       <c r="X47" s="4"/>
       <c r="Y47" s="4"/>
     </row>
-    <row r="48">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="4"/>
       <c r="B48" s="4" t="s">
         <v>53</v>
@@ -3845,7 +3833,7 @@
       <c r="X48" s="4"/>
       <c r="Y48" s="4"/>
     </row>
-    <row r="49">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -3872,7 +3860,7 @@
       <c r="X49" s="4"/>
       <c r="Y49" s="4"/>
     </row>
-    <row r="50">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>67</v>
       </c>
@@ -3901,12 +3889,12 @@
       <c r="X50" s="4"/>
       <c r="Y50" s="4"/>
     </row>
-    <row r="51">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="4"/>
       <c r="B51" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C51" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D51" s="4"/>
@@ -3932,7 +3920,7 @@
       <c r="X51" s="4"/>
       <c r="Y51" s="4"/>
     </row>
-    <row r="52">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="4"/>
       <c r="B52" s="4" t="s">
         <v>40</v>
@@ -3963,7 +3951,7 @@
       <c r="X52" s="4"/>
       <c r="Y52" s="4"/>
     </row>
-    <row r="53">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="4"/>
       <c r="B53" s="4" t="s">
         <v>29</v>
@@ -3994,7 +3982,7 @@
       <c r="X53" s="4"/>
       <c r="Y53" s="4"/>
     </row>
-    <row r="54">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" s="4" t="s">
         <v>43</v>
@@ -4025,12 +4013,12 @@
       <c r="X54" s="4"/>
       <c r="Y54" s="4"/>
     </row>
-    <row r="55">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="4"/>
       <c r="B55" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="18" t="s">
         <v>69</v>
       </c>
       <c r="D55" s="4"/>
@@ -4056,12 +4044,12 @@
       <c r="X55" s="4"/>
       <c r="Y55" s="4"/>
     </row>
-    <row r="56">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C56" s="20">
+      <c r="C56" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D56" s="4"/>
@@ -4087,12 +4075,12 @@
       <c r="X56" s="4"/>
       <c r="Y56" s="4"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C57" s="21" t="s">
+      <c r="C57" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D57" s="4"/>
@@ -4118,12 +4106,12 @@
       <c r="X57" s="4"/>
       <c r="Y57" s="4"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="4"/>
       <c r="B58" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D58" s="4"/>
@@ -4149,7 +4137,7 @@
       <c r="X58" s="4"/>
       <c r="Y58" s="4"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="4"/>
       <c r="B59" s="4" t="s">
         <v>51</v>
@@ -4180,7 +4168,7 @@
       <c r="X59" s="4"/>
       <c r="Y59" s="4"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="4"/>
       <c r="B60" s="4" t="s">
         <v>53</v>
@@ -4211,7 +4199,7 @@
       <c r="X60" s="4"/>
       <c r="Y60" s="4"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -4238,8 +4226,8 @@
       <c r="X61" s="4"/>
       <c r="Y61" s="4"/>
     </row>
-    <row r="62">
-      <c r="A62" s="18" t="s">
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="17" t="s">
         <v>70</v>
       </c>
       <c r="B62" s="4"/>
@@ -4267,12 +4255,12 @@
       <c r="X62" s="4"/>
       <c r="Y62" s="4"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C63" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D63" s="4"/>
@@ -4298,7 +4286,7 @@
       <c r="X63" s="4"/>
       <c r="Y63" s="4"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" s="4" t="s">
         <v>40</v>
@@ -4329,7 +4317,7 @@
       <c r="X64" s="4"/>
       <c r="Y64" s="4"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="4"/>
       <c r="B65" s="4" t="s">
         <v>29</v>
@@ -4360,7 +4348,7 @@
       <c r="X65" s="4"/>
       <c r="Y65" s="4"/>
     </row>
-    <row r="66">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="4"/>
       <c r="B66" s="4" t="s">
         <v>43</v>
@@ -4391,12 +4379,12 @@
       <c r="X66" s="4"/>
       <c r="Y66" s="4"/>
     </row>
-    <row r="67">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="4"/>
       <c r="B67" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C67" s="19" t="s">
+      <c r="C67" s="18" t="s">
         <v>71</v>
       </c>
       <c r="D67" s="4"/>
@@ -4422,12 +4410,12 @@
       <c r="X67" s="4"/>
       <c r="Y67" s="4"/>
     </row>
-    <row r="68">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="4"/>
       <c r="B68" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C68" s="20">
+      <c r="C68" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D68" s="4"/>
@@ -4453,12 +4441,12 @@
       <c r="X68" s="4"/>
       <c r="Y68" s="4"/>
     </row>
-    <row r="69">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="4"/>
       <c r="B69" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C69" s="21" t="s">
+      <c r="C69" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D69" s="4"/>
@@ -4484,12 +4472,12 @@
       <c r="X69" s="4"/>
       <c r="Y69" s="4"/>
     </row>
-    <row r="70">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="4"/>
       <c r="B70" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C70" s="21" t="s">
+      <c r="C70" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D70" s="4"/>
@@ -4515,7 +4503,7 @@
       <c r="X70" s="4"/>
       <c r="Y70" s="4"/>
     </row>
-    <row r="71">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="4"/>
       <c r="B71" s="4" t="s">
         <v>51</v>
@@ -4546,7 +4534,7 @@
       <c r="X71" s="4"/>
       <c r="Y71" s="4"/>
     </row>
-    <row r="72">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="4"/>
       <c r="B72" s="4" t="s">
         <v>53</v>
@@ -4577,7 +4565,7 @@
       <c r="X72" s="4"/>
       <c r="Y72" s="4"/>
     </row>
-    <row r="73">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -4604,7 +4592,7 @@
       <c r="X73" s="4"/>
       <c r="Y73" s="4"/>
     </row>
-    <row r="74">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="4" t="s">
         <v>72</v>
       </c>
@@ -4633,12 +4621,12 @@
       <c r="X74" s="4"/>
       <c r="Y74" s="4"/>
     </row>
-    <row r="75">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="4"/>
       <c r="B75" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C75" s="19" t="s">
+      <c r="C75" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D75" s="4"/>
@@ -4664,7 +4652,7 @@
       <c r="X75" s="4"/>
       <c r="Y75" s="4"/>
     </row>
-    <row r="76">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="4"/>
       <c r="B76" s="4" t="s">
         <v>40</v>
@@ -4695,12 +4683,12 @@
       <c r="X76" s="4"/>
       <c r="Y76" s="4"/>
     </row>
-    <row r="77">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="4"/>
       <c r="B77" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C77" s="19">
+      <c r="C77" s="18">
         <v>1.0</v>
       </c>
       <c r="D77" s="4"/>
@@ -4726,7 +4714,7 @@
       <c r="X77" s="4"/>
       <c r="Y77" s="4"/>
     </row>
-    <row r="78">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="4"/>
       <c r="B78" s="4" t="s">
         <v>43</v>
@@ -4755,12 +4743,12 @@
       <c r="X78" s="4"/>
       <c r="Y78" s="4"/>
     </row>
-    <row r="79">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="4"/>
       <c r="B79" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C79" s="22" t="s">
+      <c r="C79" s="21" t="s">
         <v>73</v>
       </c>
       <c r="D79" s="4"/>
@@ -4786,12 +4774,12 @@
       <c r="X79" s="4"/>
       <c r="Y79" s="4"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="4"/>
       <c r="B80" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C80" s="20">
+      <c r="C80" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D80" s="4"/>
@@ -4817,12 +4805,12 @@
       <c r="X80" s="4"/>
       <c r="Y80" s="4"/>
     </row>
-    <row r="81">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C81" s="21" t="s">
+      <c r="C81" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D81" s="4"/>
@@ -4848,12 +4836,12 @@
       <c r="X81" s="4"/>
       <c r="Y81" s="4"/>
     </row>
-    <row r="82">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="4"/>
       <c r="B82" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C82" s="21" t="s">
+      <c r="C82" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D82" s="4"/>
@@ -4879,12 +4867,12 @@
       <c r="X82" s="4"/>
       <c r="Y82" s="4"/>
     </row>
-    <row r="83">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="4"/>
       <c r="B83" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C83" s="19" t="s">
+      <c r="C83" s="18" t="s">
         <v>74</v>
       </c>
       <c r="D83" s="4"/>
@@ -4910,7 +4898,7 @@
       <c r="X83" s="4"/>
       <c r="Y83" s="4"/>
     </row>
-    <row r="84">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="4"/>
       <c r="B84" s="4" t="s">
         <v>53</v>
@@ -4941,7 +4929,7 @@
       <c r="X84" s="4"/>
       <c r="Y84" s="4"/>
     </row>
-    <row r="85">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -4968,7 +4956,7 @@
       <c r="X85" s="4"/>
       <c r="Y85" s="4"/>
     </row>
-    <row r="86">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="4" t="s">
         <v>75</v>
       </c>
@@ -4997,12 +4985,12 @@
       <c r="X86" s="4"/>
       <c r="Y86" s="4"/>
     </row>
-    <row r="87">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C87" s="19" t="s">
+      <c r="C87" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D87" s="4"/>
@@ -5028,7 +5016,7 @@
       <c r="X87" s="4"/>
       <c r="Y87" s="4"/>
     </row>
-    <row r="88">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="4"/>
       <c r="B88" s="4" t="s">
         <v>40</v>
@@ -5059,12 +5047,12 @@
       <c r="X88" s="4"/>
       <c r="Y88" s="4"/>
     </row>
-    <row r="89">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="4"/>
       <c r="B89" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C89" s="19" t="s">
+      <c r="C89" s="18" t="s">
         <v>61</v>
       </c>
       <c r="D89" s="4"/>
@@ -5090,7 +5078,7 @@
       <c r="X89" s="4"/>
       <c r="Y89" s="4"/>
     </row>
-    <row r="90">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" s="4" t="s">
         <v>43</v>
@@ -5119,12 +5107,12 @@
       <c r="X90" s="4"/>
       <c r="Y90" s="4"/>
     </row>
-    <row r="91">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="4"/>
       <c r="B91" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C91" s="19" t="s">
+      <c r="C91" s="18" t="s">
         <v>76</v>
       </c>
       <c r="D91" s="4"/>
@@ -5150,12 +5138,12 @@
       <c r="X91" s="4"/>
       <c r="Y91" s="4"/>
     </row>
-    <row r="92">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="4"/>
       <c r="B92" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C92" s="20">
+      <c r="C92" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D92" s="4"/>
@@ -5181,12 +5169,12 @@
       <c r="X92" s="4"/>
       <c r="Y92" s="4"/>
     </row>
-    <row r="93">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="4"/>
       <c r="B93" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C93" s="21" t="s">
+      <c r="C93" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D93" s="4"/>
@@ -5212,12 +5200,12 @@
       <c r="X93" s="4"/>
       <c r="Y93" s="4"/>
     </row>
-    <row r="94">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="4"/>
       <c r="B94" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C94" s="21" t="s">
+      <c r="C94" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D94" s="4"/>
@@ -5243,12 +5231,12 @@
       <c r="X94" s="4"/>
       <c r="Y94" s="4"/>
     </row>
-    <row r="95">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="4"/>
       <c r="B95" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C95" s="19" t="s">
+      <c r="C95" s="18" t="s">
         <v>77</v>
       </c>
       <c r="D95" s="4"/>
@@ -5274,7 +5262,7 @@
       <c r="X95" s="4"/>
       <c r="Y95" s="4"/>
     </row>
-    <row r="96">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="4"/>
       <c r="B96" s="4" t="s">
         <v>53</v>
@@ -5305,7 +5293,7 @@
       <c r="X96" s="4"/>
       <c r="Y96" s="4"/>
     </row>
-    <row r="97">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -5332,8 +5320,8 @@
       <c r="X97" s="4"/>
       <c r="Y97" s="4"/>
     </row>
-    <row r="98">
-      <c r="A98" s="18" t="s">
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="A98" s="17" t="s">
         <v>78</v>
       </c>
       <c r="B98" s="4"/>
@@ -5361,12 +5349,12 @@
       <c r="X98" s="4"/>
       <c r="Y98" s="4"/>
     </row>
-    <row r="99">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="4"/>
       <c r="B99" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C99" s="19" t="s">
+      <c r="C99" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D99" s="4"/>
@@ -5392,7 +5380,7 @@
       <c r="X99" s="4"/>
       <c r="Y99" s="4"/>
     </row>
-    <row r="100">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="4"/>
       <c r="B100" s="4" t="s">
         <v>40</v>
@@ -5423,12 +5411,12 @@
       <c r="X100" s="4"/>
       <c r="Y100" s="4"/>
     </row>
-    <row r="101">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="4"/>
       <c r="B101" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C101" s="19" t="s">
+      <c r="C101" s="18" t="s">
         <v>79</v>
       </c>
       <c r="D101" s="4"/>
@@ -5454,13 +5442,13 @@
       <c r="X101" s="4"/>
       <c r="Y101" s="4"/>
     </row>
-    <row r="102">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="4"/>
       <c r="B102" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C102" s="3"/>
-      <c r="D102" s="18" t="s">
+      <c r="D102" s="17" t="s">
         <v>78</v>
       </c>
       <c r="E102" s="4"/>
@@ -5485,12 +5473,12 @@
       <c r="X102" s="4"/>
       <c r="Y102" s="4"/>
     </row>
-    <row r="103">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="4"/>
       <c r="B103" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C103" s="19" t="s">
+      <c r="C103" s="18" t="s">
         <v>80</v>
       </c>
       <c r="D103" s="4"/>
@@ -5516,12 +5504,12 @@
       <c r="X103" s="4"/>
       <c r="Y103" s="4"/>
     </row>
-    <row r="104">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="4"/>
       <c r="B104" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C104" s="20">
+      <c r="C104" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D104" s="4"/>
@@ -5547,12 +5535,12 @@
       <c r="X104" s="4"/>
       <c r="Y104" s="4"/>
     </row>
-    <row r="105">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="4"/>
       <c r="B105" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C105" s="21" t="s">
+      <c r="C105" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D105" s="4"/>
@@ -5578,12 +5566,12 @@
       <c r="X105" s="4"/>
       <c r="Y105" s="4"/>
     </row>
-    <row r="106">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="4"/>
       <c r="B106" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C106" s="21" t="s">
+      <c r="C106" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D106" s="4"/>
@@ -5609,7 +5597,7 @@
       <c r="X106" s="4"/>
       <c r="Y106" s="4"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="4"/>
       <c r="B107" s="4" t="s">
         <v>51</v>
@@ -5640,7 +5628,7 @@
       <c r="X107" s="4"/>
       <c r="Y107" s="4"/>
     </row>
-    <row r="108">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="4"/>
       <c r="B108" s="4" t="s">
         <v>53</v>
@@ -5671,7 +5659,7 @@
       <c r="X108" s="4"/>
       <c r="Y108" s="4"/>
     </row>
-    <row r="109">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -5698,8 +5686,8 @@
       <c r="X109" s="4"/>
       <c r="Y109" s="4"/>
     </row>
-    <row r="110">
-      <c r="A110" s="23" t="s">
+    <row r="110" ht="15.75" customHeight="1">
+      <c r="A110" s="17" t="s">
         <v>81</v>
       </c>
       <c r="B110" s="4"/>
@@ -5727,12 +5715,12 @@
       <c r="X110" s="4"/>
       <c r="Y110" s="4"/>
     </row>
-    <row r="111">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="4"/>
       <c r="B111" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C111" s="19" t="s">
+      <c r="C111" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D111" s="4"/>
@@ -5758,7 +5746,7 @@
       <c r="X111" s="4"/>
       <c r="Y111" s="4"/>
     </row>
-    <row r="112">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="4"/>
       <c r="B112" s="4" t="s">
         <v>40</v>
@@ -5789,12 +5777,12 @@
       <c r="X112" s="4"/>
       <c r="Y112" s="4"/>
     </row>
-    <row r="113">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="4"/>
       <c r="B113" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C113" s="19" t="s">
+      <c r="C113" s="18" t="s">
         <v>61</v>
       </c>
       <c r="D113" s="4"/>
@@ -5820,7 +5808,7 @@
       <c r="X113" s="4"/>
       <c r="Y113" s="4"/>
     </row>
-    <row r="114">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="4"/>
       <c r="B114" s="4" t="s">
         <v>43</v>
@@ -5849,12 +5837,12 @@
       <c r="X114" s="4"/>
       <c r="Y114" s="4"/>
     </row>
-    <row r="115">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="4"/>
       <c r="B115" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C115" s="19" t="s">
+      <c r="C115" s="18" t="s">
         <v>82</v>
       </c>
       <c r="D115" s="4"/>
@@ -5880,12 +5868,12 @@
       <c r="X115" s="4"/>
       <c r="Y115" s="4"/>
     </row>
-    <row r="116">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="4"/>
       <c r="B116" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C116" s="20">
+      <c r="C116" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D116" s="4"/>
@@ -5911,12 +5899,12 @@
       <c r="X116" s="4"/>
       <c r="Y116" s="4"/>
     </row>
-    <row r="117">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="4"/>
       <c r="B117" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C117" s="21" t="s">
+      <c r="C117" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D117" s="4"/>
@@ -5942,12 +5930,12 @@
       <c r="X117" s="4"/>
       <c r="Y117" s="4"/>
     </row>
-    <row r="118">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="4"/>
       <c r="B118" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C118" s="21" t="s">
+      <c r="C118" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D118" s="4"/>
@@ -5973,7 +5961,7 @@
       <c r="X118" s="4"/>
       <c r="Y118" s="4"/>
     </row>
-    <row r="119">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="4"/>
       <c r="B119" s="4" t="s">
         <v>51</v>
@@ -6004,7 +5992,7 @@
       <c r="X119" s="4"/>
       <c r="Y119" s="4"/>
     </row>
-    <row r="120">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="4"/>
       <c r="B120" s="4" t="s">
         <v>53</v>
@@ -6035,7 +6023,7 @@
       <c r="X120" s="4"/>
       <c r="Y120" s="4"/>
     </row>
-    <row r="121">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -6062,7 +6050,7 @@
       <c r="X121" s="4"/>
       <c r="Y121" s="4"/>
     </row>
-    <row r="122">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="4" t="s">
         <v>83</v>
       </c>
@@ -6091,12 +6079,12 @@
       <c r="X122" s="4"/>
       <c r="Y122" s="4"/>
     </row>
-    <row r="123">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="4"/>
       <c r="B123" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C123" s="19" t="s">
+      <c r="C123" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D123" s="4"/>
@@ -6122,7 +6110,7 @@
       <c r="X123" s="4"/>
       <c r="Y123" s="4"/>
     </row>
-    <row r="124">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="4"/>
       <c r="B124" s="4" t="s">
         <v>40</v>
@@ -6153,12 +6141,12 @@
       <c r="X124" s="4"/>
       <c r="Y124" s="4"/>
     </row>
-    <row r="125">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="4"/>
       <c r="B125" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C125" s="19" t="s">
+      <c r="C125" s="18" t="s">
         <v>79</v>
       </c>
       <c r="D125" s="4"/>
@@ -6184,7 +6172,7 @@
       <c r="X125" s="4"/>
       <c r="Y125" s="4"/>
     </row>
-    <row r="126">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="4"/>
       <c r="B126" s="4" t="s">
         <v>43</v>
@@ -6215,7 +6203,7 @@
       <c r="X126" s="4"/>
       <c r="Y126" s="4"/>
     </row>
-    <row r="127">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="4"/>
       <c r="B127" s="4" t="s">
         <v>44</v>
@@ -6246,12 +6234,12 @@
       <c r="X127" s="4"/>
       <c r="Y127" s="4"/>
     </row>
-    <row r="128">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="4"/>
       <c r="B128" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C128" s="20">
+      <c r="C128" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D128" s="4"/>
@@ -6277,12 +6265,12 @@
       <c r="X128" s="4"/>
       <c r="Y128" s="4"/>
     </row>
-    <row r="129">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="4"/>
       <c r="B129" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C129" s="21" t="s">
+      <c r="C129" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D129" s="4"/>
@@ -6308,12 +6296,12 @@
       <c r="X129" s="4"/>
       <c r="Y129" s="4"/>
     </row>
-    <row r="130">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="4"/>
       <c r="B130" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C130" s="21" t="s">
+      <c r="C130" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D130" s="4"/>
@@ -6339,7 +6327,7 @@
       <c r="X130" s="4"/>
       <c r="Y130" s="4"/>
     </row>
-    <row r="131">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="4"/>
       <c r="B131" s="4" t="s">
         <v>51</v>
@@ -6370,7 +6358,7 @@
       <c r="X131" s="4"/>
       <c r="Y131" s="4"/>
     </row>
-    <row r="132">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="4"/>
       <c r="B132" s="4" t="s">
         <v>53</v>
@@ -6401,7 +6389,7 @@
       <c r="X132" s="4"/>
       <c r="Y132" s="4"/>
     </row>
-    <row r="133">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -6428,7 +6416,7 @@
       <c r="X133" s="4"/>
       <c r="Y133" s="4"/>
     </row>
-    <row r="134">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="4" t="s">
         <v>85</v>
       </c>
@@ -6457,12 +6445,12 @@
       <c r="X134" s="4"/>
       <c r="Y134" s="4"/>
     </row>
-    <row r="135">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="4"/>
       <c r="B135" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C135" s="19" t="s">
+      <c r="C135" s="18" t="s">
         <v>39</v>
       </c>
       <c r="D135" s="4"/>
@@ -6488,7 +6476,7 @@
       <c r="X135" s="4"/>
       <c r="Y135" s="4"/>
     </row>
-    <row r="136">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="4"/>
       <c r="B136" s="4" t="s">
         <v>40</v>
@@ -6519,12 +6507,12 @@
       <c r="X136" s="4"/>
       <c r="Y136" s="4"/>
     </row>
-    <row r="137">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="4"/>
       <c r="B137" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C137" s="19" t="s">
+      <c r="C137" s="18" t="s">
         <v>86</v>
       </c>
       <c r="D137" s="4"/>
@@ -6550,7 +6538,7 @@
       <c r="X137" s="4"/>
       <c r="Y137" s="4"/>
     </row>
-    <row r="138">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="4"/>
       <c r="B138" s="4" t="s">
         <v>43</v>
@@ -6579,7 +6567,7 @@
       <c r="X138" s="4"/>
       <c r="Y138" s="4"/>
     </row>
-    <row r="139">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="4"/>
       <c r="B139" s="4" t="s">
         <v>44</v>
@@ -6610,12 +6598,12 @@
       <c r="X139" s="4"/>
       <c r="Y139" s="4"/>
     </row>
-    <row r="140">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="4"/>
       <c r="B140" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C140" s="20">
+      <c r="C140" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D140" s="4"/>
@@ -6641,12 +6629,12 @@
       <c r="X140" s="4"/>
       <c r="Y140" s="4"/>
     </row>
-    <row r="141">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="4"/>
       <c r="B141" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C141" s="21" t="s">
+      <c r="C141" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D141" s="4"/>
@@ -6672,12 +6660,12 @@
       <c r="X141" s="4"/>
       <c r="Y141" s="4"/>
     </row>
-    <row r="142">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="4"/>
       <c r="B142" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C142" s="21" t="s">
+      <c r="C142" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D142" s="4"/>
@@ -6703,7 +6691,7 @@
       <c r="X142" s="4"/>
       <c r="Y142" s="4"/>
     </row>
-    <row r="143">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="4"/>
       <c r="B143" s="4" t="s">
         <v>51</v>
@@ -6734,7 +6722,7 @@
       <c r="X143" s="4"/>
       <c r="Y143" s="4"/>
     </row>
-    <row r="144">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="4"/>
       <c r="B144" s="4" t="s">
         <v>53</v>
@@ -6765,77 +6753,78 @@
       <c r="X144" s="4"/>
       <c r="Y144" s="4"/>
     </row>
-    <row r="146">
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="4" t="s">
         <v>88</v>
       </c>
       <c r="B146" s="4"/>
       <c r="C146" s="3"/>
     </row>
-    <row r="147">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="4"/>
       <c r="B147" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C147" s="19" t="s">
+      <c r="C147" s="18" t="s">
         <v>56</v>
       </c>
       <c r="D147" s="4"/>
     </row>
-    <row r="148">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="4"/>
       <c r="B148" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C148" s="24" t="s">
+      <c r="C148" s="4" t="s">
         <v>41</v>
       </c>
       <c r="D148" s="4"/>
     </row>
-    <row r="149">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="4"/>
       <c r="B149" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C149" s="19">
+      <c r="C149" s="18">
         <v>1.0</v>
       </c>
       <c r="D149" s="4"/>
     </row>
-    <row r="150">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="4"/>
       <c r="B150" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C150" s="19"/>
+      <c r="C150" s="18"/>
       <c r="D150" s="4"/>
     </row>
-    <row r="151">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="4"/>
       <c r="B151" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C151" s="19" t="s">
+      <c r="C151" s="18" t="s">
         <v>89</v>
       </c>
       <c r="D151" s="4"/>
     </row>
-    <row r="152">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="4"/>
       <c r="B152" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C152" s="19" t="s">
+      <c r="C152" s="18" t="s">
         <v>91</v>
       </c>
       <c r="D152" s="4"/>
     </row>
-    <row r="153">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="4"/>
       <c r="B153" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C153" s="25" t="s">
+      <c r="C153" s="22" t="s">
         <v>93</v>
       </c>
       <c r="D153" s="4"/>
